--- a/output/version3/test/15-5/MARL/IL/RL-RL with pt (+comm)/(RL+RL) test results.xlsx
+++ b/output/version3/test/15-5/MARL/IL/RL-RL with pt (+comm)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>594</v>
+        <v>608</v>
       </c>
       <c r="C2" t="n">
-        <v>581</v>
+        <v>635</v>
       </c>
       <c r="D2" t="n">
-        <v>686</v>
+        <v>586</v>
       </c>
       <c r="E2" t="n">
-        <v>613</v>
+        <v>638</v>
       </c>
       <c r="F2" t="n">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="G2" t="n">
         <v>602</v>
       </c>
       <c r="H2" t="n">
-        <v>569</v>
+        <v>654</v>
       </c>
       <c r="I2" t="n">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="J2" t="n">
-        <v>554</v>
+        <v>626</v>
       </c>
       <c r="K2" t="n">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="L2" t="n">
-        <v>594.1</v>
+        <v>607.8</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>742</v>
+        <v>725</v>
       </c>
       <c r="C3" t="n">
-        <v>671</v>
+        <v>750</v>
       </c>
       <c r="D3" t="n">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="E3" t="n">
-        <v>701</v>
+        <v>716</v>
       </c>
       <c r="F3" t="n">
-        <v>695</v>
+        <v>680</v>
       </c>
       <c r="G3" t="n">
-        <v>752</v>
+        <v>696</v>
       </c>
       <c r="H3" t="n">
-        <v>664</v>
+        <v>714</v>
       </c>
       <c r="I3" t="n">
-        <v>705</v>
+        <v>674</v>
       </c>
       <c r="J3" t="n">
-        <v>791</v>
+        <v>756</v>
       </c>
       <c r="K3" t="n">
-        <v>717</v>
+        <v>775</v>
       </c>
       <c r="L3" t="n">
-        <v>719.3</v>
+        <v>724.9</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>695</v>
+        <v>706</v>
       </c>
       <c r="C4" t="n">
-        <v>724</v>
+        <v>704</v>
       </c>
       <c r="D4" t="n">
-        <v>678</v>
+        <v>762</v>
       </c>
       <c r="E4" t="n">
-        <v>699</v>
+        <v>732</v>
       </c>
       <c r="F4" t="n">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="G4" t="n">
-        <v>668</v>
+        <v>753</v>
       </c>
       <c r="H4" t="n">
-        <v>656</v>
+        <v>682</v>
       </c>
       <c r="I4" t="n">
-        <v>674</v>
+        <v>697</v>
       </c>
       <c r="J4" t="n">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="K4" t="n">
-        <v>682</v>
+        <v>711</v>
       </c>
       <c r="L4" t="n">
-        <v>685.4</v>
+        <v>712.5</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>753</v>
+        <v>839</v>
       </c>
       <c r="C5" t="n">
+        <v>832</v>
+      </c>
+      <c r="D5" t="n">
+        <v>823</v>
+      </c>
+      <c r="E5" t="n">
         <v>811</v>
       </c>
-      <c r="D5" t="n">
-        <v>881</v>
-      </c>
-      <c r="E5" t="n">
-        <v>814</v>
-      </c>
       <c r="F5" t="n">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="G5" t="n">
-        <v>837</v>
+        <v>798</v>
       </c>
       <c r="H5" t="n">
-        <v>815</v>
+        <v>786</v>
       </c>
       <c r="I5" t="n">
-        <v>830</v>
+        <v>844</v>
       </c>
       <c r="J5" t="n">
-        <v>861</v>
+        <v>831</v>
       </c>
       <c r="K5" t="n">
-        <v>823</v>
+        <v>935</v>
       </c>
       <c r="L5" t="n">
-        <v>823.8</v>
+        <v>830.9</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="C6" t="n">
-        <v>628</v>
+        <v>675</v>
       </c>
       <c r="D6" t="n">
-        <v>613</v>
+        <v>661</v>
       </c>
       <c r="E6" t="n">
-        <v>665</v>
+        <v>589</v>
       </c>
       <c r="F6" t="n">
-        <v>594</v>
+        <v>713</v>
       </c>
       <c r="G6" t="n">
-        <v>669</v>
+        <v>651</v>
       </c>
       <c r="H6" t="n">
-        <v>591</v>
+        <v>696</v>
       </c>
       <c r="I6" t="n">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="J6" t="n">
-        <v>562</v>
+        <v>668</v>
       </c>
       <c r="K6" t="n">
-        <v>596</v>
+        <v>661</v>
       </c>
       <c r="L6" t="n">
-        <v>618.2</v>
+        <v>657.5</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>842</v>
+        <v>777</v>
       </c>
       <c r="C7" t="n">
-        <v>852</v>
+        <v>719</v>
       </c>
       <c r="D7" t="n">
-        <v>841</v>
+        <v>812</v>
       </c>
       <c r="E7" t="n">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="F7" t="n">
-        <v>708</v>
+        <v>667</v>
       </c>
       <c r="G7" t="n">
-        <v>752</v>
+        <v>770</v>
       </c>
       <c r="H7" t="n">
-        <v>784</v>
+        <v>760</v>
       </c>
       <c r="I7" t="n">
-        <v>723</v>
+        <v>802</v>
       </c>
       <c r="J7" t="n">
-        <v>835</v>
+        <v>677</v>
       </c>
       <c r="K7" t="n">
-        <v>714</v>
+        <v>794</v>
       </c>
       <c r="L7" t="n">
-        <v>779.3</v>
+        <v>752.1</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="C8" t="n">
-        <v>657</v>
+        <v>702</v>
       </c>
       <c r="D8" t="n">
-        <v>682</v>
+        <v>732</v>
       </c>
       <c r="E8" t="n">
+        <v>679</v>
+      </c>
+      <c r="F8" t="n">
+        <v>700</v>
+      </c>
+      <c r="G8" t="n">
+        <v>605</v>
+      </c>
+      <c r="H8" t="n">
+        <v>725</v>
+      </c>
+      <c r="I8" t="n">
         <v>693</v>
       </c>
-      <c r="F8" t="n">
-        <v>723</v>
-      </c>
-      <c r="G8" t="n">
-        <v>670</v>
-      </c>
-      <c r="H8" t="n">
-        <v>666</v>
-      </c>
-      <c r="I8" t="n">
-        <v>661</v>
-      </c>
       <c r="J8" t="n">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="K8" t="n">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="L8" t="n">
-        <v>671.9</v>
+        <v>678.4</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>704</v>
+        <v>670</v>
       </c>
       <c r="C9" t="n">
-        <v>614</v>
+        <v>659</v>
       </c>
       <c r="D9" t="n">
-        <v>647</v>
+        <v>576</v>
       </c>
       <c r="E9" t="n">
-        <v>701</v>
+        <v>587</v>
       </c>
       <c r="F9" t="n">
-        <v>665</v>
+        <v>700</v>
       </c>
       <c r="G9" t="n">
-        <v>643</v>
+        <v>709</v>
       </c>
       <c r="H9" t="n">
-        <v>635</v>
+        <v>687</v>
       </c>
       <c r="I9" t="n">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="J9" t="n">
-        <v>635</v>
+        <v>589</v>
       </c>
       <c r="K9" t="n">
-        <v>598</v>
+        <v>622</v>
       </c>
       <c r="L9" t="n">
-        <v>645.5</v>
+        <v>640.7</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="C10" t="n">
-        <v>764</v>
+        <v>752</v>
       </c>
       <c r="D10" t="n">
-        <v>684</v>
+        <v>765</v>
       </c>
       <c r="E10" t="n">
-        <v>755</v>
+        <v>737</v>
       </c>
       <c r="F10" t="n">
-        <v>744</v>
+        <v>785</v>
       </c>
       <c r="G10" t="n">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="H10" t="n">
-        <v>730</v>
+        <v>757</v>
       </c>
       <c r="I10" t="n">
-        <v>787</v>
+        <v>689</v>
       </c>
       <c r="J10" t="n">
-        <v>709</v>
+        <v>696</v>
       </c>
       <c r="K10" t="n">
-        <v>722</v>
+        <v>754</v>
       </c>
       <c r="L10" t="n">
-        <v>734.4</v>
+        <v>738.4</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>707</v>
+        <v>720</v>
       </c>
       <c r="C11" t="n">
-        <v>719</v>
+        <v>704</v>
       </c>
       <c r="D11" t="n">
-        <v>682</v>
+        <v>697</v>
       </c>
       <c r="E11" t="n">
-        <v>779</v>
+        <v>716</v>
       </c>
       <c r="F11" t="n">
-        <v>786</v>
+        <v>843</v>
       </c>
       <c r="G11" t="n">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="H11" t="n">
-        <v>671</v>
+        <v>743</v>
       </c>
       <c r="I11" t="n">
-        <v>773</v>
+        <v>709</v>
       </c>
       <c r="J11" t="n">
-        <v>788</v>
+        <v>659</v>
       </c>
       <c r="K11" t="n">
-        <v>738</v>
+        <v>762</v>
       </c>
       <c r="L11" t="n">
-        <v>744.7</v>
+        <v>735.4</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>687</v>
+        <v>601</v>
       </c>
       <c r="C12" t="n">
-        <v>749</v>
+        <v>654</v>
       </c>
       <c r="D12" t="n">
-        <v>655</v>
+        <v>622</v>
       </c>
       <c r="E12" t="n">
-        <v>637</v>
+        <v>657</v>
       </c>
       <c r="F12" t="n">
-        <v>667</v>
+        <v>705</v>
       </c>
       <c r="G12" t="n">
-        <v>737</v>
+        <v>691</v>
       </c>
       <c r="H12" t="n">
-        <v>717</v>
+        <v>698</v>
       </c>
       <c r="I12" t="n">
-        <v>600</v>
+        <v>647</v>
       </c>
       <c r="J12" t="n">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="K12" t="n">
-        <v>655</v>
+        <v>740</v>
       </c>
       <c r="L12" t="n">
-        <v>680.2</v>
+        <v>670.9</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="C13" t="n">
-        <v>609</v>
+        <v>588</v>
       </c>
       <c r="D13" t="n">
-        <v>565</v>
+        <v>533</v>
       </c>
       <c r="E13" t="n">
-        <v>527</v>
+        <v>603</v>
       </c>
       <c r="F13" t="n">
-        <v>569</v>
+        <v>586</v>
       </c>
       <c r="G13" t="n">
-        <v>597</v>
+        <v>530</v>
       </c>
       <c r="H13" t="n">
-        <v>536</v>
+        <v>546</v>
       </c>
       <c r="I13" t="n">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="J13" t="n">
-        <v>562</v>
+        <v>612</v>
       </c>
       <c r="K13" t="n">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="L13" t="n">
-        <v>563.2</v>
+        <v>568.3</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>672</v>
+        <v>639</v>
       </c>
       <c r="C14" t="n">
+        <v>642</v>
+      </c>
+      <c r="D14" t="n">
+        <v>620</v>
+      </c>
+      <c r="E14" t="n">
+        <v>632</v>
+      </c>
+      <c r="F14" t="n">
+        <v>679</v>
+      </c>
+      <c r="G14" t="n">
+        <v>660</v>
+      </c>
+      <c r="H14" t="n">
+        <v>654</v>
+      </c>
+      <c r="I14" t="n">
         <v>638</v>
       </c>
-      <c r="D14" t="n">
-        <v>647</v>
-      </c>
-      <c r="E14" t="n">
-        <v>670</v>
-      </c>
-      <c r="F14" t="n">
-        <v>688</v>
-      </c>
-      <c r="G14" t="n">
-        <v>639</v>
-      </c>
-      <c r="H14" t="n">
-        <v>600</v>
-      </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
+        <v>726</v>
+      </c>
+      <c r="K14" t="n">
         <v>663</v>
       </c>
-      <c r="J14" t="n">
-        <v>665</v>
-      </c>
-      <c r="K14" t="n">
-        <v>728</v>
-      </c>
       <c r="L14" t="n">
-        <v>661</v>
+        <v>655.3</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>634</v>
+        <v>740</v>
       </c>
       <c r="C15" t="n">
-        <v>682</v>
+        <v>713</v>
       </c>
       <c r="D15" t="n">
-        <v>684</v>
+        <v>726</v>
       </c>
       <c r="E15" t="n">
-        <v>749</v>
+        <v>638</v>
       </c>
       <c r="F15" t="n">
-        <v>749</v>
+        <v>767</v>
       </c>
       <c r="G15" t="n">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H15" t="n">
-        <v>733</v>
+        <v>703</v>
       </c>
       <c r="I15" t="n">
-        <v>647</v>
+        <v>779</v>
       </c>
       <c r="J15" t="n">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="K15" t="n">
-        <v>687</v>
+        <v>663</v>
       </c>
       <c r="L15" t="n">
-        <v>700</v>
+        <v>715.6</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>704</v>
+        <v>678</v>
       </c>
       <c r="C16" t="n">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="D16" t="n">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="E16" t="n">
-        <v>671</v>
+        <v>652</v>
       </c>
       <c r="F16" t="n">
-        <v>618</v>
+        <v>637</v>
       </c>
       <c r="G16" t="n">
-        <v>778</v>
+        <v>677</v>
       </c>
       <c r="H16" t="n">
-        <v>677</v>
+        <v>656</v>
       </c>
       <c r="I16" t="n">
-        <v>729</v>
+        <v>650</v>
       </c>
       <c r="J16" t="n">
-        <v>665</v>
+        <v>724</v>
       </c>
       <c r="K16" t="n">
-        <v>622</v>
+        <v>597</v>
       </c>
       <c r="L16" t="n">
-        <v>680.8</v>
+        <v>659.7</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>679</v>
+        <v>830</v>
       </c>
       <c r="C17" t="n">
-        <v>704</v>
+        <v>816</v>
       </c>
       <c r="D17" t="n">
-        <v>833</v>
+        <v>659</v>
       </c>
       <c r="E17" t="n">
-        <v>754</v>
+        <v>724</v>
       </c>
       <c r="F17" t="n">
-        <v>767</v>
+        <v>805</v>
       </c>
       <c r="G17" t="n">
-        <v>781</v>
+        <v>750</v>
       </c>
       <c r="H17" t="n">
-        <v>872</v>
+        <v>836</v>
       </c>
       <c r="I17" t="n">
-        <v>781</v>
+        <v>708</v>
       </c>
       <c r="J17" t="n">
-        <v>823</v>
+        <v>728</v>
       </c>
       <c r="K17" t="n">
-        <v>828</v>
+        <v>790</v>
       </c>
       <c r="L17" t="n">
-        <v>782.2</v>
+        <v>764.6</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>629</v>
+        <v>615</v>
       </c>
       <c r="C18" t="n">
-        <v>741</v>
+        <v>645</v>
       </c>
       <c r="D18" t="n">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="E18" t="n">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F18" t="n">
-        <v>654</v>
+        <v>687</v>
       </c>
       <c r="G18" t="n">
-        <v>616</v>
+        <v>573</v>
       </c>
       <c r="H18" t="n">
-        <v>722</v>
+        <v>684</v>
       </c>
       <c r="I18" t="n">
-        <v>647</v>
+        <v>627</v>
       </c>
       <c r="J18" t="n">
-        <v>623</v>
+        <v>663</v>
       </c>
       <c r="K18" t="n">
-        <v>720</v>
+        <v>675</v>
       </c>
       <c r="L18" t="n">
-        <v>662.2</v>
+        <v>644.4</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>770</v>
+        <v>649</v>
       </c>
       <c r="C19" t="n">
-        <v>603</v>
+        <v>637</v>
       </c>
       <c r="D19" t="n">
-        <v>694</v>
+        <v>627</v>
       </c>
       <c r="E19" t="n">
-        <v>621</v>
+        <v>805</v>
       </c>
       <c r="F19" t="n">
-        <v>727</v>
+        <v>760</v>
       </c>
       <c r="G19" t="n">
-        <v>681</v>
+        <v>648</v>
       </c>
       <c r="H19" t="n">
-        <v>608</v>
+        <v>736</v>
       </c>
       <c r="I19" t="n">
-        <v>577</v>
+        <v>684</v>
       </c>
       <c r="J19" t="n">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="K19" t="n">
-        <v>713</v>
+        <v>669</v>
       </c>
       <c r="L19" t="n">
-        <v>668.2</v>
+        <v>691.1</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>633</v>
+        <v>762</v>
       </c>
       <c r="C20" t="n">
-        <v>723</v>
+        <v>595</v>
       </c>
       <c r="D20" t="n">
-        <v>604</v>
+        <v>672</v>
       </c>
       <c r="E20" t="n">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="F20" t="n">
-        <v>667</v>
+        <v>589</v>
       </c>
       <c r="G20" t="n">
-        <v>630</v>
+        <v>672</v>
       </c>
       <c r="H20" t="n">
-        <v>691</v>
+        <v>660</v>
       </c>
       <c r="I20" t="n">
-        <v>671</v>
+        <v>555</v>
       </c>
       <c r="J20" t="n">
-        <v>587</v>
+        <v>635</v>
       </c>
       <c r="K20" t="n">
-        <v>617</v>
+        <v>703</v>
       </c>
       <c r="L20" t="n">
-        <v>646.5</v>
+        <v>649.2</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>638</v>
+        <v>618</v>
       </c>
       <c r="C21" t="n">
-        <v>649</v>
+        <v>680</v>
       </c>
       <c r="D21" t="n">
-        <v>631</v>
+        <v>724</v>
       </c>
       <c r="E21" t="n">
-        <v>661</v>
+        <v>702</v>
       </c>
       <c r="F21" t="n">
-        <v>597</v>
+        <v>614</v>
       </c>
       <c r="G21" t="n">
-        <v>689</v>
+        <v>662</v>
       </c>
       <c r="H21" t="n">
-        <v>656</v>
+        <v>624</v>
       </c>
       <c r="I21" t="n">
-        <v>672</v>
+        <v>625</v>
       </c>
       <c r="J21" t="n">
-        <v>756</v>
+        <v>592</v>
       </c>
       <c r="K21" t="n">
-        <v>577</v>
+        <v>658</v>
       </c>
       <c r="L21" t="n">
-        <v>652.6</v>
+        <v>649.9</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="C22" t="n">
-        <v>526</v>
+        <v>656</v>
       </c>
       <c r="D22" t="n">
-        <v>514</v>
+        <v>591</v>
       </c>
       <c r="E22" t="n">
-        <v>556</v>
+        <v>569</v>
       </c>
       <c r="F22" t="n">
-        <v>583</v>
+        <v>628</v>
       </c>
       <c r="G22" t="n">
-        <v>569</v>
+        <v>600</v>
       </c>
       <c r="H22" t="n">
-        <v>678</v>
+        <v>566</v>
       </c>
       <c r="I22" t="n">
-        <v>532</v>
+        <v>563</v>
       </c>
       <c r="J22" t="n">
-        <v>523</v>
+        <v>560</v>
       </c>
       <c r="K22" t="n">
-        <v>534</v>
+        <v>647</v>
       </c>
       <c r="L22" t="n">
-        <v>558.7</v>
+        <v>596.2</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="C23" t="n">
-        <v>716</v>
+        <v>781</v>
       </c>
       <c r="D23" t="n">
-        <v>668</v>
+        <v>781</v>
       </c>
       <c r="E23" t="n">
-        <v>676</v>
+        <v>703</v>
       </c>
       <c r="F23" t="n">
-        <v>635</v>
+        <v>719</v>
       </c>
       <c r="G23" t="n">
-        <v>695</v>
+        <v>705</v>
       </c>
       <c r="H23" t="n">
-        <v>656</v>
+        <v>677</v>
       </c>
       <c r="I23" t="n">
-        <v>725</v>
+        <v>644</v>
       </c>
       <c r="J23" t="n">
-        <v>633</v>
+        <v>647</v>
       </c>
       <c r="K23" t="n">
-        <v>724</v>
+        <v>645</v>
       </c>
       <c r="L23" t="n">
-        <v>680</v>
+        <v>696.8</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="C24" t="n">
-        <v>790</v>
+        <v>689</v>
       </c>
       <c r="D24" t="n">
-        <v>794</v>
+        <v>751</v>
       </c>
       <c r="E24" t="n">
-        <v>685</v>
+        <v>657</v>
       </c>
       <c r="F24" t="n">
-        <v>694</v>
+        <v>676</v>
       </c>
       <c r="G24" t="n">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="H24" t="n">
-        <v>719</v>
+        <v>687</v>
       </c>
       <c r="I24" t="n">
-        <v>629</v>
+        <v>697</v>
       </c>
       <c r="J24" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="K24" t="n">
-        <v>781</v>
+        <v>607</v>
       </c>
       <c r="L24" t="n">
-        <v>712.2</v>
+        <v>679.3</v>
       </c>
     </row>
     <row r="25">
@@ -1348,34 +1348,34 @@
         <v>620</v>
       </c>
       <c r="C25" t="n">
-        <v>655</v>
+        <v>594</v>
       </c>
       <c r="D25" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="E25" t="n">
-        <v>687</v>
+        <v>657</v>
       </c>
       <c r="F25" t="n">
-        <v>650</v>
+        <v>669</v>
       </c>
       <c r="G25" t="n">
-        <v>673</v>
+        <v>601</v>
       </c>
       <c r="H25" t="n">
-        <v>638</v>
+        <v>684</v>
       </c>
       <c r="I25" t="n">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="J25" t="n">
-        <v>693</v>
+        <v>605</v>
       </c>
       <c r="K25" t="n">
-        <v>645</v>
+        <v>573</v>
       </c>
       <c r="L25" t="n">
-        <v>653.7</v>
+        <v>627</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="C26" t="n">
-        <v>723</v>
+        <v>743</v>
       </c>
       <c r="D26" t="n">
-        <v>662</v>
+        <v>707</v>
       </c>
       <c r="E26" t="n">
-        <v>708</v>
+        <v>696</v>
       </c>
       <c r="F26" t="n">
+        <v>728</v>
+      </c>
+      <c r="G26" t="n">
+        <v>686</v>
+      </c>
+      <c r="H26" t="n">
+        <v>726</v>
+      </c>
+      <c r="I26" t="n">
+        <v>663</v>
+      </c>
+      <c r="J26" t="n">
         <v>725</v>
       </c>
-      <c r="G26" t="n">
-        <v>645</v>
-      </c>
-      <c r="H26" t="n">
-        <v>694</v>
-      </c>
-      <c r="I26" t="n">
-        <v>690</v>
-      </c>
-      <c r="J26" t="n">
-        <v>764</v>
-      </c>
       <c r="K26" t="n">
-        <v>741</v>
+        <v>687</v>
       </c>
       <c r="L26" t="n">
-        <v>709</v>
+        <v>709.5</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>753</v>
+        <v>655</v>
       </c>
       <c r="C27" t="n">
-        <v>777</v>
+        <v>791</v>
       </c>
       <c r="D27" t="n">
-        <v>699</v>
+        <v>733</v>
       </c>
       <c r="E27" t="n">
+        <v>775</v>
+      </c>
+      <c r="F27" t="n">
         <v>743</v>
       </c>
-      <c r="F27" t="n">
-        <v>766</v>
-      </c>
       <c r="G27" t="n">
-        <v>783</v>
+        <v>742</v>
       </c>
       <c r="H27" t="n">
-        <v>807</v>
+        <v>698</v>
       </c>
       <c r="I27" t="n">
-        <v>814</v>
+        <v>692</v>
       </c>
       <c r="J27" t="n">
-        <v>750</v>
+        <v>695</v>
       </c>
       <c r="K27" t="n">
-        <v>690</v>
+        <v>762</v>
       </c>
       <c r="L27" t="n">
-        <v>758.2</v>
+        <v>728.6</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>664</v>
+        <v>647</v>
       </c>
       <c r="C28" t="n">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="D28" t="n">
-        <v>628</v>
+        <v>582</v>
       </c>
       <c r="E28" t="n">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="F28" t="n">
-        <v>657</v>
+        <v>620</v>
       </c>
       <c r="G28" t="n">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="H28" t="n">
-        <v>652</v>
+        <v>612</v>
       </c>
       <c r="I28" t="n">
-        <v>613</v>
+        <v>583</v>
       </c>
       <c r="J28" t="n">
-        <v>600</v>
+        <v>586</v>
       </c>
       <c r="K28" t="n">
-        <v>573</v>
+        <v>622</v>
       </c>
       <c r="L28" t="n">
-        <v>622.5</v>
+        <v>608.8</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>612</v>
+        <v>670</v>
       </c>
       <c r="C29" t="n">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D29" t="n">
-        <v>622</v>
+        <v>665</v>
       </c>
       <c r="E29" t="n">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="F29" t="n">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="G29" t="n">
-        <v>651</v>
+        <v>667</v>
       </c>
       <c r="H29" t="n">
-        <v>669</v>
+        <v>648</v>
       </c>
       <c r="I29" t="n">
-        <v>760</v>
+        <v>635</v>
       </c>
       <c r="J29" t="n">
-        <v>685</v>
+        <v>664</v>
       </c>
       <c r="K29" t="n">
-        <v>734</v>
+        <v>594</v>
       </c>
       <c r="L29" t="n">
-        <v>665</v>
+        <v>647.4</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="C30" t="n">
-        <v>652</v>
+        <v>591</v>
       </c>
       <c r="D30" t="n">
-        <v>694</v>
+        <v>630</v>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>678</v>
       </c>
       <c r="F30" t="n">
-        <v>697</v>
+        <v>645</v>
       </c>
       <c r="G30" t="n">
-        <v>752</v>
+        <v>651</v>
       </c>
       <c r="H30" t="n">
-        <v>673</v>
+        <v>621</v>
       </c>
       <c r="I30" t="n">
-        <v>712</v>
+        <v>771</v>
       </c>
       <c r="J30" t="n">
-        <v>652</v>
+        <v>809</v>
       </c>
       <c r="K30" t="n">
-        <v>705</v>
+        <v>662</v>
       </c>
       <c r="L30" t="n">
-        <v>691.8</v>
+        <v>680.2</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>658</v>
+        <v>685</v>
       </c>
       <c r="C31" t="n">
-        <v>700</v>
+        <v>732</v>
       </c>
       <c r="D31" t="n">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="E31" t="n">
-        <v>712</v>
+        <v>647</v>
       </c>
       <c r="F31" t="n">
-        <v>690</v>
+        <v>657</v>
       </c>
       <c r="G31" t="n">
         <v>643</v>
       </c>
       <c r="H31" t="n">
-        <v>756</v>
+        <v>659</v>
       </c>
       <c r="I31" t="n">
-        <v>717</v>
+        <v>684</v>
       </c>
       <c r="J31" t="n">
-        <v>747</v>
+        <v>694</v>
       </c>
       <c r="K31" t="n">
-        <v>630</v>
+        <v>693</v>
       </c>
       <c r="L31" t="n">
-        <v>693.9</v>
+        <v>677.7</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="C32" t="n">
-        <v>597</v>
+        <v>581</v>
       </c>
       <c r="D32" t="n">
+        <v>604</v>
+      </c>
+      <c r="E32" t="n">
+        <v>660</v>
+      </c>
+      <c r="F32" t="n">
         <v>609</v>
       </c>
-      <c r="E32" t="n">
-        <v>561</v>
-      </c>
-      <c r="F32" t="n">
-        <v>631</v>
-      </c>
       <c r="G32" t="n">
-        <v>666</v>
+        <v>609</v>
       </c>
       <c r="H32" t="n">
-        <v>540</v>
+        <v>603</v>
       </c>
       <c r="I32" t="n">
-        <v>739</v>
+        <v>604</v>
       </c>
       <c r="J32" t="n">
-        <v>683</v>
+        <v>604</v>
       </c>
       <c r="K32" t="n">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="L32" t="n">
-        <v>620</v>
+        <v>603.2</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>683</v>
+        <v>760</v>
       </c>
       <c r="C33" t="n">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="D33" t="n">
-        <v>697</v>
+        <v>772</v>
       </c>
       <c r="E33" t="n">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="F33" t="n">
-        <v>843</v>
+        <v>717</v>
       </c>
       <c r="G33" t="n">
-        <v>699</v>
+        <v>742</v>
       </c>
       <c r="H33" t="n">
-        <v>738</v>
+        <v>795</v>
       </c>
       <c r="I33" t="n">
-        <v>692</v>
+        <v>763</v>
       </c>
       <c r="J33" t="n">
-        <v>680</v>
+        <v>792</v>
       </c>
       <c r="K33" t="n">
-        <v>792</v>
+        <v>669</v>
       </c>
       <c r="L33" t="n">
-        <v>723.3</v>
+        <v>742.1</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>559</v>
+        <v>590</v>
       </c>
       <c r="C34" t="n">
+        <v>615</v>
+      </c>
+      <c r="D34" t="n">
+        <v>649</v>
+      </c>
+      <c r="E34" t="n">
+        <v>589</v>
+      </c>
+      <c r="F34" t="n">
+        <v>637</v>
+      </c>
+      <c r="G34" t="n">
         <v>633</v>
       </c>
-      <c r="D34" t="n">
-        <v>567</v>
-      </c>
-      <c r="E34" t="n">
+      <c r="H34" t="n">
+        <v>568</v>
+      </c>
+      <c r="I34" t="n">
+        <v>669</v>
+      </c>
+      <c r="J34" t="n">
         <v>563</v>
       </c>
-      <c r="F34" t="n">
-        <v>656</v>
-      </c>
-      <c r="G34" t="n">
-        <v>588</v>
-      </c>
-      <c r="H34" t="n">
-        <v>577</v>
-      </c>
-      <c r="I34" t="n">
-        <v>654</v>
-      </c>
-      <c r="J34" t="n">
-        <v>729</v>
-      </c>
       <c r="K34" t="n">
-        <v>583</v>
+        <v>602</v>
       </c>
       <c r="L34" t="n">
-        <v>610.9</v>
+        <v>611.5</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>678</v>
+        <v>780</v>
       </c>
       <c r="C35" t="n">
-        <v>681</v>
+        <v>748</v>
       </c>
       <c r="D35" t="n">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="E35" t="n">
-        <v>709</v>
+        <v>823</v>
       </c>
       <c r="F35" t="n">
-        <v>817</v>
+        <v>715</v>
       </c>
       <c r="G35" t="n">
-        <v>816</v>
+        <v>733</v>
       </c>
       <c r="H35" t="n">
-        <v>851</v>
+        <v>773</v>
       </c>
       <c r="I35" t="n">
-        <v>764</v>
+        <v>719</v>
       </c>
       <c r="J35" t="n">
-        <v>729</v>
+        <v>747</v>
       </c>
       <c r="K35" t="n">
-        <v>749</v>
+        <v>797</v>
       </c>
       <c r="L35" t="n">
-        <v>753.4</v>
+        <v>757</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>589</v>
+        <v>574</v>
       </c>
       <c r="C36" t="n">
-        <v>588</v>
+        <v>632</v>
       </c>
       <c r="D36" t="n">
-        <v>611</v>
+        <v>585</v>
       </c>
       <c r="E36" t="n">
-        <v>530</v>
+        <v>620</v>
       </c>
       <c r="F36" t="n">
-        <v>569</v>
+        <v>535</v>
       </c>
       <c r="G36" t="n">
-        <v>619</v>
+        <v>602</v>
       </c>
       <c r="H36" t="n">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="I36" t="n">
-        <v>532</v>
+        <v>614</v>
       </c>
       <c r="J36" t="n">
-        <v>612</v>
+        <v>580</v>
       </c>
       <c r="K36" t="n">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="L36" t="n">
-        <v>579.3</v>
+        <v>589.7</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>756</v>
+        <v>848</v>
       </c>
       <c r="C37" t="n">
-        <v>699</v>
+        <v>751</v>
       </c>
       <c r="D37" t="n">
-        <v>799</v>
+        <v>697</v>
       </c>
       <c r="E37" t="n">
-        <v>662</v>
+        <v>643</v>
       </c>
       <c r="F37" t="n">
-        <v>684</v>
+        <v>649</v>
       </c>
       <c r="G37" t="n">
-        <v>656</v>
+        <v>688</v>
       </c>
       <c r="H37" t="n">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="I37" t="n">
-        <v>728</v>
+        <v>762</v>
       </c>
       <c r="J37" t="n">
-        <v>672</v>
+        <v>683</v>
       </c>
       <c r="K37" t="n">
-        <v>676</v>
+        <v>626</v>
       </c>
       <c r="L37" t="n">
-        <v>701.6</v>
+        <v>703.2</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>704</v>
+        <v>721</v>
       </c>
       <c r="C38" t="n">
-        <v>718</v>
+        <v>663</v>
       </c>
       <c r="D38" t="n">
-        <v>678</v>
+        <v>644</v>
       </c>
       <c r="E38" t="n">
-        <v>692</v>
+        <v>735</v>
       </c>
       <c r="F38" t="n">
-        <v>682</v>
+        <v>729</v>
       </c>
       <c r="G38" t="n">
-        <v>756</v>
+        <v>702</v>
       </c>
       <c r="H38" t="n">
-        <v>683</v>
+        <v>706</v>
       </c>
       <c r="I38" t="n">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="J38" t="n">
-        <v>680</v>
+        <v>613</v>
       </c>
       <c r="K38" t="n">
-        <v>732</v>
+        <v>757</v>
       </c>
       <c r="L38" t="n">
-        <v>700.3</v>
+        <v>694.9</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>498</v>
+        <v>611</v>
       </c>
       <c r="C39" t="n">
-        <v>598</v>
+        <v>559</v>
       </c>
       <c r="D39" t="n">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="E39" t="n">
-        <v>534</v>
+        <v>653</v>
       </c>
       <c r="F39" t="n">
-        <v>600</v>
+        <v>649</v>
       </c>
       <c r="G39" t="n">
-        <v>526</v>
+        <v>671</v>
       </c>
       <c r="H39" t="n">
-        <v>571</v>
+        <v>540</v>
       </c>
       <c r="I39" t="n">
-        <v>594</v>
+        <v>561</v>
       </c>
       <c r="J39" t="n">
-        <v>643</v>
+        <v>570</v>
       </c>
       <c r="K39" t="n">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="L39" t="n">
-        <v>566.6</v>
+        <v>591.1</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>707</v>
+        <v>779</v>
       </c>
       <c r="C40" t="n">
-        <v>710</v>
+        <v>631</v>
       </c>
       <c r="D40" t="n">
-        <v>682</v>
+        <v>695</v>
       </c>
       <c r="E40" t="n">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="F40" t="n">
-        <v>613</v>
+        <v>631</v>
       </c>
       <c r="G40" t="n">
-        <v>784</v>
+        <v>697</v>
       </c>
       <c r="H40" t="n">
-        <v>660</v>
+        <v>727</v>
       </c>
       <c r="I40" t="n">
-        <v>655</v>
+        <v>672</v>
       </c>
       <c r="J40" t="n">
-        <v>676</v>
+        <v>751</v>
       </c>
       <c r="K40" t="n">
-        <v>642</v>
+        <v>614</v>
       </c>
       <c r="L40" t="n">
-        <v>681.6</v>
+        <v>689.2</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>619</v>
+        <v>665</v>
       </c>
       <c r="C41" t="n">
-        <v>683</v>
+        <v>736</v>
       </c>
       <c r="D41" t="n">
-        <v>653</v>
+        <v>691</v>
       </c>
       <c r="E41" t="n">
-        <v>633</v>
+        <v>758</v>
       </c>
       <c r="F41" t="n">
-        <v>646</v>
+        <v>604</v>
       </c>
       <c r="G41" t="n">
-        <v>692</v>
+        <v>606</v>
       </c>
       <c r="H41" t="n">
         <v>658</v>
       </c>
       <c r="I41" t="n">
-        <v>616</v>
+        <v>627</v>
       </c>
       <c r="J41" t="n">
-        <v>665</v>
+        <v>626</v>
       </c>
       <c r="K41" t="n">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="L41" t="n">
-        <v>646.4</v>
+        <v>656.5</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>608</v>
+        <v>646</v>
       </c>
       <c r="C42" t="n">
-        <v>523</v>
+        <v>598</v>
       </c>
       <c r="D42" t="n">
-        <v>641</v>
+        <v>611</v>
       </c>
       <c r="E42" t="n">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="F42" t="n">
-        <v>592</v>
+        <v>615</v>
       </c>
       <c r="G42" t="n">
-        <v>711</v>
+        <v>589</v>
       </c>
       <c r="H42" t="n">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="I42" t="n">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="J42" t="n">
-        <v>527</v>
+        <v>619</v>
       </c>
       <c r="K42" t="n">
-        <v>569</v>
+        <v>591</v>
       </c>
       <c r="L42" t="n">
-        <v>604.5</v>
+        <v>612.7</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>689</v>
+        <v>623</v>
       </c>
       <c r="C43" t="n">
-        <v>719</v>
+        <v>610</v>
       </c>
       <c r="D43" t="n">
-        <v>707</v>
+        <v>649</v>
       </c>
       <c r="E43" t="n">
-        <v>669</v>
+        <v>650</v>
       </c>
       <c r="F43" t="n">
-        <v>624</v>
+        <v>702</v>
       </c>
       <c r="G43" t="n">
-        <v>691</v>
+        <v>655</v>
       </c>
       <c r="H43" t="n">
-        <v>670</v>
+        <v>703</v>
       </c>
       <c r="I43" t="n">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="J43" t="n">
-        <v>676</v>
+        <v>641</v>
       </c>
       <c r="K43" t="n">
-        <v>732</v>
+        <v>615</v>
       </c>
       <c r="L43" t="n">
-        <v>682.8</v>
+        <v>648.9</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
+        <v>694</v>
+      </c>
+      <c r="C44" t="n">
+        <v>755</v>
+      </c>
+      <c r="D44" t="n">
         <v>728</v>
       </c>
-      <c r="C44" t="n">
-        <v>706</v>
-      </c>
-      <c r="D44" t="n">
-        <v>659</v>
-      </c>
       <c r="E44" t="n">
-        <v>695</v>
+        <v>754</v>
       </c>
       <c r="F44" t="n">
-        <v>654</v>
+        <v>717</v>
       </c>
       <c r="G44" t="n">
-        <v>749</v>
+        <v>726</v>
       </c>
       <c r="H44" t="n">
+        <v>717</v>
+      </c>
+      <c r="I44" t="n">
+        <v>726</v>
+      </c>
+      <c r="J44" t="n">
         <v>676</v>
       </c>
-      <c r="I44" t="n">
-        <v>682</v>
-      </c>
-      <c r="J44" t="n">
-        <v>771</v>
-      </c>
       <c r="K44" t="n">
-        <v>715</v>
+        <v>668</v>
       </c>
       <c r="L44" t="n">
-        <v>703.5</v>
+        <v>716.1</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>609</v>
+        <v>553</v>
       </c>
       <c r="C45" t="n">
-        <v>586</v>
+        <v>661</v>
       </c>
       <c r="D45" t="n">
-        <v>613</v>
+        <v>565</v>
       </c>
       <c r="E45" t="n">
-        <v>624</v>
+        <v>592</v>
       </c>
       <c r="F45" t="n">
-        <v>568</v>
+        <v>601</v>
       </c>
       <c r="G45" t="n">
-        <v>563</v>
+        <v>665</v>
       </c>
       <c r="H45" t="n">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="I45" t="n">
-        <v>586</v>
+        <v>634</v>
       </c>
       <c r="J45" t="n">
-        <v>628</v>
+        <v>576</v>
       </c>
       <c r="K45" t="n">
-        <v>573</v>
+        <v>557</v>
       </c>
       <c r="L45" t="n">
-        <v>592.5</v>
+        <v>598.3</v>
       </c>
     </row>
     <row r="46">
@@ -2146,34 +2146,34 @@
         <v>613</v>
       </c>
       <c r="C46" t="n">
-        <v>653</v>
+        <v>587</v>
       </c>
       <c r="D46" t="n">
-        <v>567</v>
+        <v>651</v>
       </c>
       <c r="E46" t="n">
-        <v>696</v>
+        <v>648</v>
       </c>
       <c r="F46" t="n">
-        <v>658</v>
+        <v>645</v>
       </c>
       <c r="G46" t="n">
-        <v>604</v>
+        <v>680</v>
       </c>
       <c r="H46" t="n">
-        <v>612</v>
+        <v>665</v>
       </c>
       <c r="I46" t="n">
-        <v>558</v>
+        <v>711</v>
       </c>
       <c r="J46" t="n">
-        <v>598</v>
+        <v>663</v>
       </c>
       <c r="K46" t="n">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="L46" t="n">
-        <v>615.7</v>
+        <v>646.6</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>758</v>
+        <v>834</v>
       </c>
       <c r="C47" t="n">
-        <v>718</v>
+        <v>815</v>
       </c>
       <c r="D47" t="n">
-        <v>761</v>
+        <v>726</v>
       </c>
       <c r="E47" t="n">
-        <v>772</v>
+        <v>667</v>
       </c>
       <c r="F47" t="n">
-        <v>662</v>
+        <v>719</v>
       </c>
       <c r="G47" t="n">
-        <v>682</v>
+        <v>722</v>
       </c>
       <c r="H47" t="n">
-        <v>716</v>
+        <v>727</v>
       </c>
       <c r="I47" t="n">
-        <v>757</v>
+        <v>773</v>
       </c>
       <c r="J47" t="n">
-        <v>739</v>
+        <v>835</v>
       </c>
       <c r="K47" t="n">
-        <v>776</v>
+        <v>840</v>
       </c>
       <c r="L47" t="n">
-        <v>734.1</v>
+        <v>765.8</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>665</v>
+        <v>681</v>
       </c>
       <c r="C48" t="n">
-        <v>638</v>
+        <v>623</v>
       </c>
       <c r="D48" t="n">
-        <v>645</v>
+        <v>628</v>
       </c>
       <c r="E48" t="n">
-        <v>575</v>
+        <v>725</v>
       </c>
       <c r="F48" t="n">
-        <v>662</v>
+        <v>689</v>
       </c>
       <c r="G48" t="n">
-        <v>638</v>
+        <v>725</v>
       </c>
       <c r="H48" t="n">
-        <v>638</v>
+        <v>623</v>
       </c>
       <c r="I48" t="n">
-        <v>638</v>
+        <v>540</v>
       </c>
       <c r="J48" t="n">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="K48" t="n">
-        <v>748</v>
+        <v>654</v>
       </c>
       <c r="L48" t="n">
-        <v>648.9</v>
+        <v>653.6</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>864</v>
+        <v>791</v>
       </c>
       <c r="C49" t="n">
-        <v>769</v>
+        <v>792</v>
       </c>
       <c r="D49" t="n">
-        <v>804</v>
+        <v>715</v>
       </c>
       <c r="E49" t="n">
-        <v>732</v>
+        <v>741</v>
       </c>
       <c r="F49" t="n">
-        <v>791</v>
+        <v>854</v>
       </c>
       <c r="G49" t="n">
-        <v>867</v>
+        <v>808</v>
       </c>
       <c r="H49" t="n">
-        <v>721</v>
+        <v>813</v>
       </c>
       <c r="I49" t="n">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="J49" t="n">
-        <v>819</v>
+        <v>760</v>
       </c>
       <c r="K49" t="n">
-        <v>808</v>
+        <v>788</v>
       </c>
       <c r="L49" t="n">
-        <v>800.2</v>
+        <v>788.4</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>670</v>
+        <v>625</v>
       </c>
       <c r="C50" t="n">
-        <v>665</v>
+        <v>694</v>
       </c>
       <c r="D50" t="n">
-        <v>693</v>
+        <v>643</v>
       </c>
       <c r="E50" t="n">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="F50" t="n">
-        <v>670</v>
+        <v>628</v>
       </c>
       <c r="G50" t="n">
-        <v>605</v>
+        <v>616</v>
       </c>
       <c r="H50" t="n">
-        <v>639</v>
+        <v>571</v>
       </c>
       <c r="I50" t="n">
-        <v>624</v>
+        <v>646</v>
       </c>
       <c r="J50" t="n">
-        <v>664</v>
+        <v>644</v>
       </c>
       <c r="K50" t="n">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="L50" t="n">
-        <v>652.6</v>
+        <v>635.2</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>699</v>
+        <v>751</v>
       </c>
       <c r="C51" t="n">
-        <v>694</v>
+        <v>678</v>
       </c>
       <c r="D51" t="n">
-        <v>751</v>
+        <v>689</v>
       </c>
       <c r="E51" t="n">
-        <v>798</v>
+        <v>776</v>
       </c>
       <c r="F51" t="n">
-        <v>583</v>
+        <v>698</v>
       </c>
       <c r="G51" t="n">
-        <v>666</v>
+        <v>675</v>
       </c>
       <c r="H51" t="n">
-        <v>681</v>
+        <v>626</v>
       </c>
       <c r="I51" t="n">
-        <v>643</v>
+        <v>675</v>
       </c>
       <c r="J51" t="n">
-        <v>654</v>
+        <v>708</v>
       </c>
       <c r="K51" t="n">
-        <v>632</v>
+        <v>717</v>
       </c>
       <c r="L51" t="n">
-        <v>680.1</v>
+        <v>699.3</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>672.14</v>
+        <v>681.98</v>
       </c>
       <c r="C52" t="n">
-        <v>677.66</v>
+        <v>680.86</v>
       </c>
       <c r="D52" t="n">
-        <v>675.4400000000001</v>
+        <v>672.1</v>
       </c>
       <c r="E52" t="n">
-        <v>670.08</v>
+        <v>680</v>
       </c>
       <c r="F52" t="n">
-        <v>673.84</v>
+        <v>681.72</v>
       </c>
       <c r="G52" t="n">
-        <v>684.7</v>
+        <v>675.7</v>
       </c>
       <c r="H52" t="n">
-        <v>672.1799999999999</v>
+        <v>676.72</v>
       </c>
       <c r="I52" t="n">
-        <v>673.62</v>
+        <v>670.5599999999999</v>
       </c>
       <c r="J52" t="n">
-        <v>681.66</v>
+        <v>672.3</v>
       </c>
       <c r="K52" t="n">
-        <v>670.04</v>
+        <v>668.54</v>
       </c>
       <c r="L52" t="n">
-        <v>675.136</v>
+        <v>676.048</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4.045514106750488</v>
+        <v>4.29831075668335</v>
       </c>
       <c r="C2" t="n">
-        <v>4.118305444717407</v>
+        <v>4.101827144622803</v>
       </c>
       <c r="D2" t="n">
-        <v>4.554125308990479</v>
+        <v>3.99062442779541</v>
       </c>
       <c r="E2" t="n">
-        <v>5.072434902191162</v>
+        <v>4.467376470565796</v>
       </c>
       <c r="F2" t="n">
-        <v>4.079272508621216</v>
+        <v>4.235466480255127</v>
       </c>
       <c r="G2" t="n">
-        <v>4.207134485244751</v>
+        <v>4.319245338439941</v>
       </c>
       <c r="H2" t="n">
-        <v>4.034967660903931</v>
+        <v>4.098829507827759</v>
       </c>
       <c r="I2" t="n">
-        <v>4.144151210784912</v>
+        <v>4.001106739044189</v>
       </c>
       <c r="J2" t="n">
-        <v>4.323283910751343</v>
+        <v>4.310274839401245</v>
       </c>
       <c r="K2" t="n">
-        <v>4.087083101272583</v>
+        <v>4.029502630233765</v>
       </c>
       <c r="L2" t="n">
-        <v>4.266627264022827</v>
+        <v>4.185256433486939</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>4.328909158706665</v>
+        <v>4.702276706695557</v>
       </c>
       <c r="C3" t="n">
-        <v>4.431281566619873</v>
+        <v>4.83346152305603</v>
       </c>
       <c r="D3" t="n">
-        <v>4.697145462036133</v>
+        <v>4.655866622924805</v>
       </c>
       <c r="E3" t="n">
-        <v>4.406423807144165</v>
+        <v>4.331724882125854</v>
       </c>
       <c r="F3" t="n">
-        <v>4.570471286773682</v>
+        <v>4.655867338180542</v>
       </c>
       <c r="G3" t="n">
-        <v>4.546929597854614</v>
+        <v>4.513749837875366</v>
       </c>
       <c r="H3" t="n">
-        <v>4.369438409805298</v>
+        <v>4.455901145935059</v>
       </c>
       <c r="I3" t="n">
-        <v>4.934629917144775</v>
+        <v>4.45838475227356</v>
       </c>
       <c r="J3" t="n">
-        <v>4.644778490066528</v>
+        <v>5.117182493209839</v>
       </c>
       <c r="K3" t="n">
-        <v>4.783970594406128</v>
+        <v>4.846296072006226</v>
       </c>
       <c r="L3" t="n">
-        <v>4.571397829055786</v>
+        <v>4.657071137428284</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>4.724606990814209</v>
+        <v>4.399259328842163</v>
       </c>
       <c r="C4" t="n">
-        <v>4.816376447677612</v>
+        <v>4.8361656665802</v>
       </c>
       <c r="D4" t="n">
-        <v>4.319698572158813</v>
+        <v>4.85661792755127</v>
       </c>
       <c r="E4" t="n">
-        <v>4.476242542266846</v>
+        <v>4.666605234146118</v>
       </c>
       <c r="F4" t="n">
-        <v>4.626708507537842</v>
+        <v>4.670095920562744</v>
       </c>
       <c r="G4" t="n">
-        <v>4.515762567520142</v>
+        <v>4.761863470077515</v>
       </c>
       <c r="H4" t="n">
-        <v>4.541414260864258</v>
+        <v>4.863626480102539</v>
       </c>
       <c r="I4" t="n">
-        <v>4.682572364807129</v>
+        <v>4.545160055160522</v>
       </c>
       <c r="J4" t="n">
-        <v>4.549079895019531</v>
+        <v>4.487798690795898</v>
       </c>
       <c r="K4" t="n">
-        <v>4.97545862197876</v>
+        <v>4.549673318862915</v>
       </c>
       <c r="L4" t="n">
-        <v>4.622792077064514</v>
+        <v>4.663686609268188</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>5.227194547653198</v>
+        <v>5.165542364120483</v>
       </c>
       <c r="C5" t="n">
-        <v>5.249335050582886</v>
+        <v>5.304680585861206</v>
       </c>
       <c r="D5" t="n">
-        <v>5.263637781143188</v>
+        <v>4.882710933685303</v>
       </c>
       <c r="E5" t="n">
-        <v>4.919982433319092</v>
+        <v>5.112478971481323</v>
       </c>
       <c r="F5" t="n">
-        <v>5.014124155044556</v>
+        <v>5.81615138053894</v>
       </c>
       <c r="G5" t="n">
-        <v>4.999959945678711</v>
+        <v>5.060585737228394</v>
       </c>
       <c r="H5" t="n">
-        <v>5.060989379882812</v>
+        <v>4.9329514503479</v>
       </c>
       <c r="I5" t="n">
-        <v>4.975016832351685</v>
+        <v>5.699958562850952</v>
       </c>
       <c r="J5" t="n">
-        <v>5.308054685592651</v>
+        <v>4.99427342414856</v>
       </c>
       <c r="K5" t="n">
-        <v>4.721951246261597</v>
+        <v>5.416192531585693</v>
       </c>
       <c r="L5" t="n">
-        <v>5.074024605751037</v>
+        <v>5.238552594184876</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>4.072858333587646</v>
+        <v>3.919506311416626</v>
       </c>
       <c r="C6" t="n">
-        <v>4.034080982208252</v>
+        <v>3.935458421707153</v>
       </c>
       <c r="D6" t="n">
-        <v>4.304866313934326</v>
+        <v>3.83273720741272</v>
       </c>
       <c r="E6" t="n">
-        <v>3.848543167114258</v>
+        <v>3.73994779586792</v>
       </c>
       <c r="F6" t="n">
-        <v>3.73039698600769</v>
+        <v>3.970372676849365</v>
       </c>
       <c r="G6" t="n">
-        <v>3.966733455657959</v>
+        <v>3.74346137046814</v>
       </c>
       <c r="H6" t="n">
-        <v>3.896877527236938</v>
+        <v>3.979854106903076</v>
       </c>
       <c r="I6" t="n">
-        <v>4.082314252853394</v>
+        <v>3.913519382476807</v>
       </c>
       <c r="J6" t="n">
-        <v>3.761596918106079</v>
+        <v>4.165871858596802</v>
       </c>
       <c r="K6" t="n">
-        <v>3.809756994247437</v>
+        <v>3.917517423629761</v>
       </c>
       <c r="L6" t="n">
-        <v>3.950802493095398</v>
+        <v>3.911824655532837</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>5.015104055404663</v>
+        <v>5.008548498153687</v>
       </c>
       <c r="C7" t="n">
-        <v>5.068346261978149</v>
+        <v>5.201759338378906</v>
       </c>
       <c r="D7" t="n">
-        <v>5.033930540084839</v>
+        <v>4.670091390609741</v>
       </c>
       <c r="E7" t="n">
-        <v>4.782901048660278</v>
+        <v>5.079550504684448</v>
       </c>
       <c r="F7" t="n">
-        <v>4.37119460105896</v>
+        <v>4.520291805267334</v>
       </c>
       <c r="G7" t="n">
-        <v>4.795384645462036</v>
+        <v>5.042641401290894</v>
       </c>
       <c r="H7" t="n">
-        <v>5.25916314125061</v>
+        <v>5.073617458343506</v>
       </c>
       <c r="I7" t="n">
-        <v>4.571900844573975</v>
+        <v>4.969332218170166</v>
       </c>
       <c r="J7" t="n">
-        <v>4.723230123519897</v>
+        <v>4.698510646820068</v>
       </c>
       <c r="K7" t="n">
-        <v>4.570107936859131</v>
+        <v>4.62719202041626</v>
       </c>
       <c r="L7" t="n">
-        <v>4.819126319885254</v>
+        <v>4.889153528213501</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>3.977184057235718</v>
+        <v>3.872635364532471</v>
       </c>
       <c r="C8" t="n">
-        <v>4.05947470664978</v>
+        <v>4.192330121994019</v>
       </c>
       <c r="D8" t="n">
-        <v>4.01157808303833</v>
+        <v>4.355384588241577</v>
       </c>
       <c r="E8" t="n">
-        <v>4.092593908309937</v>
+        <v>4.365898370742798</v>
       </c>
       <c r="F8" t="n">
-        <v>4.314178466796875</v>
+        <v>4.166862487792969</v>
       </c>
       <c r="G8" t="n">
-        <v>3.96513819694519</v>
+        <v>3.877608060836792</v>
       </c>
       <c r="H8" t="n">
-        <v>4.184502363204956</v>
+        <v>4.366869211196899</v>
       </c>
       <c r="I8" t="n">
-        <v>4.124963283538818</v>
+        <v>3.958394050598145</v>
       </c>
       <c r="J8" t="n">
-        <v>4.060256958007812</v>
+        <v>4.282572031021118</v>
       </c>
       <c r="K8" t="n">
-        <v>3.983340501785278</v>
+        <v>4.070614099502563</v>
       </c>
       <c r="L8" t="n">
-        <v>4.07732105255127</v>
+        <v>4.150916838645935</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>4.202457189559937</v>
+        <v>4.102529287338257</v>
       </c>
       <c r="C9" t="n">
-        <v>4.070288419723511</v>
+        <v>3.91752552986145</v>
       </c>
       <c r="D9" t="n">
-        <v>3.847557067871094</v>
+        <v>3.741971731185913</v>
       </c>
       <c r="E9" t="n">
-        <v>4.319470882415771</v>
+        <v>3.834215879440308</v>
       </c>
       <c r="F9" t="n">
-        <v>4.224069595336914</v>
+        <v>3.838216543197632</v>
       </c>
       <c r="G9" t="n">
-        <v>3.764171361923218</v>
+        <v>4.095547437667847</v>
       </c>
       <c r="H9" t="n">
-        <v>3.813950777053833</v>
+        <v>4.09704852104187</v>
       </c>
       <c r="I9" t="n">
-        <v>3.973990678787231</v>
+        <v>4.071122169494629</v>
       </c>
       <c r="J9" t="n">
-        <v>4.046060800552368</v>
+        <v>4.034724473953247</v>
       </c>
       <c r="K9" t="n">
-        <v>3.773983240127563</v>
+        <v>3.620784521102905</v>
       </c>
       <c r="L9" t="n">
-        <v>4.003600001335144</v>
+        <v>3.935368609428406</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>4.896598815917969</v>
+        <v>4.934418678283691</v>
       </c>
       <c r="C10" t="n">
-        <v>5.219199180603027</v>
+        <v>4.794777154922485</v>
       </c>
       <c r="D10" t="n">
-        <v>4.621201753616333</v>
+        <v>4.901485919952393</v>
       </c>
       <c r="E10" t="n">
-        <v>4.665988922119141</v>
+        <v>4.512994050979614</v>
       </c>
       <c r="F10" t="n">
-        <v>5.260379076004028</v>
+        <v>5.100498914718628</v>
       </c>
       <c r="G10" t="n">
-        <v>4.751634359359741</v>
+        <v>5.003252267837524</v>
       </c>
       <c r="H10" t="n">
-        <v>4.786160707473755</v>
+        <v>5.253116846084595</v>
       </c>
       <c r="I10" t="n">
-        <v>4.855170249938965</v>
+        <v>4.970810651779175</v>
       </c>
       <c r="J10" t="n">
-        <v>4.914376497268677</v>
+        <v>4.685551166534424</v>
       </c>
       <c r="K10" t="n">
-        <v>4.778099536895752</v>
+        <v>5.112473964691162</v>
       </c>
       <c r="L10" t="n">
-        <v>4.874880909919739</v>
+        <v>4.926937961578369</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>4.33036208152771</v>
+        <v>4.663651704788208</v>
       </c>
       <c r="C11" t="n">
-        <v>4.375643968582153</v>
+        <v>4.525964498519897</v>
       </c>
       <c r="D11" t="n">
-        <v>4.481958389282227</v>
+        <v>4.348397254943848</v>
       </c>
       <c r="E11" t="n">
-        <v>4.525624990463257</v>
+        <v>4.451149702072144</v>
       </c>
       <c r="F11" t="n">
-        <v>4.542228221893311</v>
+        <v>4.842639207839966</v>
       </c>
       <c r="G11" t="n">
-        <v>4.43852424621582</v>
+        <v>4.214253664016724</v>
       </c>
       <c r="H11" t="n">
-        <v>4.360821723937988</v>
+        <v>4.600292205810547</v>
       </c>
       <c r="I11" t="n">
-        <v>4.794703006744385</v>
+        <v>4.386817693710327</v>
       </c>
       <c r="J11" t="n">
-        <v>4.679813861846924</v>
+        <v>4.325479984283447</v>
       </c>
       <c r="K11" t="n">
-        <v>4.649821758270264</v>
+        <v>4.557877540588379</v>
       </c>
       <c r="L11" t="n">
-        <v>4.517950224876404</v>
+        <v>4.491652345657348</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>3.939373016357422</v>
+        <v>3.860649585723877</v>
       </c>
       <c r="C12" t="n">
-        <v>4.377626419067383</v>
+        <v>4.181354761123657</v>
       </c>
       <c r="D12" t="n">
-        <v>4.022368431091309</v>
+        <v>4.144917964935303</v>
       </c>
       <c r="E12" t="n">
-        <v>4.05200719833374</v>
+        <v>3.965379238128662</v>
       </c>
       <c r="F12" t="n">
-        <v>3.909114360809326</v>
+        <v>4.187337398529053</v>
       </c>
       <c r="G12" t="n">
-        <v>4.42814564704895</v>
+        <v>4.437180519104004</v>
       </c>
       <c r="H12" t="n">
-        <v>4.202207326889038</v>
+        <v>4.279112100601196</v>
       </c>
       <c r="I12" t="n">
-        <v>3.893864393234253</v>
+        <v>4.06713604927063</v>
       </c>
       <c r="J12" t="n">
-        <v>4.01063060760498</v>
+        <v>4.4187331199646</v>
       </c>
       <c r="K12" t="n">
-        <v>4.257508516311646</v>
+        <v>3.999837398529053</v>
       </c>
       <c r="L12" t="n">
-        <v>4.109284591674805</v>
+        <v>4.154163813591003</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>4.086036682128906</v>
+        <v>3.967371225357056</v>
       </c>
       <c r="C13" t="n">
-        <v>4.168548345565796</v>
+        <v>3.906546831130981</v>
       </c>
       <c r="D13" t="n">
-        <v>4.016919612884521</v>
+        <v>4.038556575775146</v>
       </c>
       <c r="E13" t="n">
-        <v>4.068383455276489</v>
+        <v>4.106825828552246</v>
       </c>
       <c r="F13" t="n">
-        <v>3.988551616668701</v>
+        <v>4.271887063980103</v>
       </c>
       <c r="G13" t="n">
-        <v>3.954622745513916</v>
+        <v>3.796124458312988</v>
       </c>
       <c r="H13" t="n">
-        <v>3.808215141296387</v>
+        <v>4.048974752426147</v>
       </c>
       <c r="I13" t="n">
-        <v>4.006424903869629</v>
+        <v>3.968153238296509</v>
       </c>
       <c r="J13" t="n">
-        <v>3.700544357299805</v>
+        <v>3.945724964141846</v>
       </c>
       <c r="K13" t="n">
-        <v>3.938316583633423</v>
+        <v>3.961194753646851</v>
       </c>
       <c r="L13" t="n">
-        <v>3.973656344413757</v>
+        <v>4.001135969161988</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>4.466488361358643</v>
+        <v>3.80211353302002</v>
       </c>
       <c r="C14" t="n">
-        <v>4.119040489196777</v>
+        <v>4.161182403564453</v>
       </c>
       <c r="D14" t="n">
-        <v>4.276031732559204</v>
+        <v>4.411503076553345</v>
       </c>
       <c r="E14" t="n">
-        <v>4.231657981872559</v>
+        <v>4.053448438644409</v>
       </c>
       <c r="F14" t="n">
-        <v>4.035619497299194</v>
+        <v>4.136505126953125</v>
       </c>
       <c r="G14" t="n">
-        <v>3.858736991882324</v>
+        <v>4.422719717025757</v>
       </c>
       <c r="H14" t="n">
-        <v>4.241427898406982</v>
+        <v>4.188339471817017</v>
       </c>
       <c r="I14" t="n">
-        <v>3.780078649520874</v>
+        <v>4.225263118743896</v>
       </c>
       <c r="J14" t="n">
-        <v>3.978435516357422</v>
+        <v>4.185840606689453</v>
       </c>
       <c r="K14" t="n">
-        <v>4.629720449447632</v>
+        <v>3.962890386581421</v>
       </c>
       <c r="L14" t="n">
-        <v>4.161723756790161</v>
+        <v>4.154980587959289</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>4.652825355529785</v>
+        <v>4.500016212463379</v>
       </c>
       <c r="C15" t="n">
-        <v>4.641036510467529</v>
+        <v>4.494041442871094</v>
       </c>
       <c r="D15" t="n">
-        <v>4.30328631401062</v>
+        <v>4.532957315444946</v>
       </c>
       <c r="E15" t="n">
-        <v>4.741786241531372</v>
+        <v>4.696550846099854</v>
       </c>
       <c r="F15" t="n">
-        <v>4.633239507675171</v>
+        <v>4.915077209472656</v>
       </c>
       <c r="G15" t="n">
-        <v>4.530077934265137</v>
+        <v>4.558132171630859</v>
       </c>
       <c r="H15" t="n">
-        <v>4.796941995620728</v>
+        <v>4.426469326019287</v>
       </c>
       <c r="I15" t="n">
-        <v>4.403380632400513</v>
+        <v>5.135127067565918</v>
       </c>
       <c r="J15" t="n">
-        <v>4.513008117675781</v>
+        <v>4.397577524185181</v>
       </c>
       <c r="K15" t="n">
-        <v>4.647139549255371</v>
+        <v>4.51674485206604</v>
       </c>
       <c r="L15" t="n">
-        <v>4.5862722158432</v>
+        <v>4.617269396781921</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>4.325141429901123</v>
+        <v>4.388585805892944</v>
       </c>
       <c r="C16" t="n">
-        <v>4.473836660385132</v>
+        <v>4.514756679534912</v>
       </c>
       <c r="D16" t="n">
-        <v>4.23083758354187</v>
+        <v>4.19507360458374</v>
       </c>
       <c r="E16" t="n">
-        <v>4.135607719421387</v>
+        <v>4.171142339706421</v>
       </c>
       <c r="F16" t="n">
-        <v>4.076456069946289</v>
+        <v>4.178614854812622</v>
       </c>
       <c r="G16" t="n">
-        <v>4.431274890899658</v>
+        <v>4.164156198501587</v>
       </c>
       <c r="H16" t="n">
-        <v>4.217946290969849</v>
+        <v>4.482832908630371</v>
       </c>
       <c r="I16" t="n">
-        <v>4.57311224937439</v>
+        <v>4.155685186386108</v>
       </c>
       <c r="J16" t="n">
-        <v>4.051677227020264</v>
+        <v>4.164166212081909</v>
       </c>
       <c r="K16" t="n">
-        <v>4.104380130767822</v>
+        <v>4.309262990951538</v>
       </c>
       <c r="L16" t="n">
-        <v>4.262027025222778</v>
+        <v>4.272427678108215</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>4.486009836196899</v>
+        <v>4.501767158508301</v>
       </c>
       <c r="C17" t="n">
-        <v>4.276433944702148</v>
+        <v>4.843400716781616</v>
       </c>
       <c r="D17" t="n">
-        <v>4.62910008430481</v>
+        <v>4.263386487960815</v>
       </c>
       <c r="E17" t="n">
-        <v>4.54079532623291</v>
+        <v>4.608020067214966</v>
       </c>
       <c r="F17" t="n">
-        <v>4.557746648788452</v>
+        <v>4.748129367828369</v>
       </c>
       <c r="G17" t="n">
-        <v>4.359957695007324</v>
+        <v>4.464902877807617</v>
       </c>
       <c r="H17" t="n">
-        <v>4.986022472381592</v>
+        <v>4.829421520233154</v>
       </c>
       <c r="I17" t="n">
-        <v>4.437555551528931</v>
+        <v>4.456399202346802</v>
       </c>
       <c r="J17" t="n">
-        <v>4.870532751083374</v>
+        <v>4.435975551605225</v>
       </c>
       <c r="K17" t="n">
-        <v>4.859323263168335</v>
+        <v>4.871332168579102</v>
       </c>
       <c r="L17" t="n">
-        <v>4.600347757339478</v>
+        <v>4.602273511886597</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>3.812313079833984</v>
+        <v>3.862454414367676</v>
       </c>
       <c r="C18" t="n">
-        <v>4.141940116882324</v>
+        <v>3.730900526046753</v>
       </c>
       <c r="D18" t="n">
-        <v>3.74062180519104</v>
+        <v>3.855693101882935</v>
       </c>
       <c r="E18" t="n">
-        <v>3.63133978843689</v>
+        <v>3.843189716339111</v>
       </c>
       <c r="F18" t="n">
-        <v>3.828118085861206</v>
+        <v>3.907544374465942</v>
       </c>
       <c r="G18" t="n">
-        <v>3.616744518280029</v>
+        <v>3.688095569610596</v>
       </c>
       <c r="H18" t="n">
-        <v>3.753710269927979</v>
+        <v>3.929473161697388</v>
       </c>
       <c r="I18" t="n">
-        <v>3.970930576324463</v>
+        <v>3.747932434082031</v>
       </c>
       <c r="J18" t="n">
-        <v>3.768041372299194</v>
+        <v>3.842725992202759</v>
       </c>
       <c r="K18" t="n">
-        <v>3.757421255111694</v>
+        <v>4.056660413742065</v>
       </c>
       <c r="L18" t="n">
-        <v>3.80211808681488</v>
+        <v>3.846466970443726</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>4.976929903030396</v>
+        <v>4.488053560256958</v>
       </c>
       <c r="C19" t="n">
-        <v>4.402312755584717</v>
+        <v>4.369863510131836</v>
       </c>
       <c r="D19" t="n">
-        <v>4.843544244766235</v>
+        <v>4.476587533950806</v>
       </c>
       <c r="E19" t="n">
-        <v>4.626163721084595</v>
+        <v>4.764867544174194</v>
       </c>
       <c r="F19" t="n">
-        <v>4.809627294540405</v>
+        <v>4.770345211029053</v>
       </c>
       <c r="G19" t="n">
-        <v>4.532392263412476</v>
+        <v>4.694527864456177</v>
       </c>
       <c r="H19" t="n">
-        <v>4.347477674484253</v>
+        <v>4.618202924728394</v>
       </c>
       <c r="I19" t="n">
-        <v>4.429044246673584</v>
+        <v>4.608246088027954</v>
       </c>
       <c r="J19" t="n">
-        <v>5.730993032455444</v>
+        <v>4.557379722595215</v>
       </c>
       <c r="K19" t="n">
-        <v>5.826610088348389</v>
+        <v>4.366387605667114</v>
       </c>
       <c r="L19" t="n">
-        <v>4.85250952243805</v>
+        <v>4.57144615650177</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>5.297459602355957</v>
+        <v>4.659131050109863</v>
       </c>
       <c r="C20" t="n">
-        <v>4.613974809646606</v>
+        <v>4.006795406341553</v>
       </c>
       <c r="D20" t="n">
-        <v>4.667078256607056</v>
+        <v>4.256149053573608</v>
       </c>
       <c r="E20" t="n">
-        <v>5.027609825134277</v>
+        <v>4.086567640304565</v>
       </c>
       <c r="F20" t="n">
-        <v>4.813899517059326</v>
+        <v>4.258636474609375</v>
       </c>
       <c r="G20" t="n">
-        <v>4.737450361251831</v>
+        <v>4.218235492706299</v>
       </c>
       <c r="H20" t="n">
-        <v>5.381163120269775</v>
+        <v>4.115007400512695</v>
       </c>
       <c r="I20" t="n">
-        <v>4.385124683380127</v>
+        <v>4.051673173904419</v>
       </c>
       <c r="J20" t="n">
-        <v>4.189229726791382</v>
+        <v>4.28557562828064</v>
       </c>
       <c r="K20" t="n">
-        <v>6.124497890472412</v>
+        <v>4.489052295684814</v>
       </c>
       <c r="L20" t="n">
-        <v>4.923748779296875</v>
+        <v>4.242682361602784</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>4.450626373291016</v>
+        <v>4.497038602828979</v>
       </c>
       <c r="C21" t="n">
-        <v>4.304528474807739</v>
+        <v>4.547890186309814</v>
       </c>
       <c r="D21" t="n">
-        <v>4.670592308044434</v>
+        <v>4.405776023864746</v>
       </c>
       <c r="E21" t="n">
-        <v>4.360879421234131</v>
+        <v>4.738913536071777</v>
       </c>
       <c r="F21" t="n">
-        <v>4.215370178222656</v>
+        <v>4.285128355026245</v>
       </c>
       <c r="G21" t="n">
-        <v>4.511765480041504</v>
+        <v>4.329957246780396</v>
       </c>
       <c r="H21" t="n">
-        <v>4.369098424911499</v>
+        <v>4.140956878662109</v>
       </c>
       <c r="I21" t="n">
-        <v>4.221003770828247</v>
+        <v>4.326480388641357</v>
       </c>
       <c r="J21" t="n">
-        <v>4.595085382461548</v>
+        <v>4.255160570144653</v>
       </c>
       <c r="K21" t="n">
-        <v>4.237948179244995</v>
+        <v>4.234725952148438</v>
       </c>
       <c r="L21" t="n">
-        <v>4.393689799308777</v>
+        <v>4.376202774047852</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>3.880892276763916</v>
+        <v>4.684584379196167</v>
       </c>
       <c r="C22" t="n">
-        <v>4.148230314254761</v>
+        <v>4.547930955886841</v>
       </c>
       <c r="D22" t="n">
-        <v>3.990092754364014</v>
+        <v>4.374859571456909</v>
       </c>
       <c r="E22" t="n">
-        <v>4.268391132354736</v>
+        <v>4.396803617477417</v>
       </c>
       <c r="F22" t="n">
-        <v>4.406507253646851</v>
+        <v>4.637166023254395</v>
       </c>
       <c r="G22" t="n">
-        <v>4.118759870529175</v>
+        <v>4.013771057128906</v>
       </c>
       <c r="H22" t="n">
-        <v>4.296334028244019</v>
+        <v>4.365362882614136</v>
       </c>
       <c r="I22" t="n">
-        <v>4.284350633621216</v>
+        <v>4.417244434356689</v>
       </c>
       <c r="J22" t="n">
-        <v>4.227978944778442</v>
+        <v>4.099537134170532</v>
       </c>
       <c r="K22" t="n">
-        <v>4.308271646499634</v>
+        <v>4.613244533538818</v>
       </c>
       <c r="L22" t="n">
-        <v>4.192980885505676</v>
+        <v>4.415050458908081</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>4.674315214157104</v>
+        <v>4.341429471969604</v>
       </c>
       <c r="C23" t="n">
-        <v>4.416486263275146</v>
+        <v>4.996247529983521</v>
       </c>
       <c r="D23" t="n">
-        <v>4.46037483215332</v>
+        <v>4.806754589080811</v>
       </c>
       <c r="E23" t="n">
-        <v>4.478837013244629</v>
+        <v>4.26810359954834</v>
       </c>
       <c r="F23" t="n">
-        <v>4.178625822067261</v>
+        <v>4.394781827926636</v>
       </c>
       <c r="G23" t="n">
-        <v>4.364623069763184</v>
+        <v>4.558402538299561</v>
       </c>
       <c r="H23" t="n">
-        <v>4.174123048782349</v>
+        <v>4.628185749053955</v>
       </c>
       <c r="I23" t="n">
-        <v>4.888258218765259</v>
+        <v>4.366372108459473</v>
       </c>
       <c r="J23" t="n">
-        <v>4.106796741485596</v>
+        <v>4.12620210647583</v>
       </c>
       <c r="K23" t="n">
-        <v>4.293308973312378</v>
+        <v>4.047686815261841</v>
       </c>
       <c r="L23" t="n">
-        <v>4.403574919700622</v>
+        <v>4.453416633605957</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>4.307327747344971</v>
+        <v>4.303558111190796</v>
       </c>
       <c r="C24" t="n">
-        <v>4.848879098892212</v>
+        <v>4.120568513870239</v>
       </c>
       <c r="D24" t="n">
-        <v>4.506782054901123</v>
+        <v>4.389832258224487</v>
       </c>
       <c r="E24" t="n">
-        <v>4.3780837059021</v>
+        <v>4.371851682662964</v>
       </c>
       <c r="F24" t="n">
-        <v>4.260421752929688</v>
+        <v>4.353437185287476</v>
       </c>
       <c r="G24" t="n">
-        <v>4.289318323135376</v>
+        <v>4.154892683029175</v>
       </c>
       <c r="H24" t="n">
-        <v>4.381093740463257</v>
+        <v>4.07610559463501</v>
       </c>
       <c r="I24" t="n">
-        <v>4.04296612739563</v>
+        <v>4.512000560760498</v>
       </c>
       <c r="J24" t="n">
-        <v>4.203068494796753</v>
+        <v>4.515997648239136</v>
       </c>
       <c r="K24" t="n">
-        <v>4.786354303359985</v>
+        <v>4.383877038955688</v>
       </c>
       <c r="L24" t="n">
-        <v>4.400429534912109</v>
+        <v>4.318212127685547</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>3.829214811325073</v>
+        <v>3.736979246139526</v>
       </c>
       <c r="C25" t="n">
-        <v>3.950398683547974</v>
+        <v>3.759439706802368</v>
       </c>
       <c r="D25" t="n">
-        <v>3.68509840965271</v>
+        <v>4.00678277015686</v>
       </c>
       <c r="E25" t="n">
-        <v>3.893556118011475</v>
+        <v>3.813266754150391</v>
       </c>
       <c r="F25" t="n">
-        <v>4.137949228286743</v>
+        <v>3.762901782989502</v>
       </c>
       <c r="G25" t="n">
-        <v>3.964896202087402</v>
+        <v>3.701056480407715</v>
       </c>
       <c r="H25" t="n">
-        <v>4.015755414962769</v>
+        <v>3.803293704986572</v>
       </c>
       <c r="I25" t="n">
-        <v>4.110012531280518</v>
+        <v>4.020750761032104</v>
       </c>
       <c r="J25" t="n">
-        <v>3.992856979370117</v>
+        <v>3.922497272491455</v>
       </c>
       <c r="K25" t="n">
-        <v>3.804295063018799</v>
+        <v>3.79182767868042</v>
       </c>
       <c r="L25" t="n">
-        <v>3.938403344154358</v>
+        <v>3.831879615783691</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>4.388797044754028</v>
+        <v>4.333459138870239</v>
       </c>
       <c r="C26" t="n">
-        <v>5.24762225151062</v>
+        <v>4.632156372070312</v>
       </c>
       <c r="D26" t="n">
-        <v>4.835681915283203</v>
+        <v>4.506031036376953</v>
       </c>
       <c r="E26" t="n">
-        <v>4.51397705078125</v>
+        <v>4.435708284378052</v>
       </c>
       <c r="F26" t="n">
-        <v>4.795779705047607</v>
+        <v>4.525512218475342</v>
       </c>
       <c r="G26" t="n">
-        <v>4.708490610122681</v>
+        <v>4.508007526397705</v>
       </c>
       <c r="H26" t="n">
-        <v>4.55685830116272</v>
+        <v>4.582816123962402</v>
       </c>
       <c r="I26" t="n">
-        <v>4.533470392227173</v>
+        <v>4.639666318893433</v>
       </c>
       <c r="J26" t="n">
-        <v>4.653142929077148</v>
+        <v>4.59575891494751</v>
       </c>
       <c r="K26" t="n">
-        <v>4.63719630241394</v>
+        <v>4.852148056030273</v>
       </c>
       <c r="L26" t="n">
-        <v>4.687101650238037</v>
+        <v>4.561126399040222</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>4.740424871444702</v>
+        <v>4.666093587875366</v>
       </c>
       <c r="C27" t="n">
-        <v>4.963825464248657</v>
+        <v>5.209714651107788</v>
       </c>
       <c r="D27" t="n">
-        <v>4.921935558319092</v>
+        <v>5.027553558349609</v>
       </c>
       <c r="E27" t="n">
-        <v>4.644658088684082</v>
+        <v>4.877296686172485</v>
       </c>
       <c r="F27" t="n">
-        <v>4.917953252792358</v>
+        <v>4.781553745269775</v>
       </c>
       <c r="G27" t="n">
-        <v>6.16997766494751</v>
+        <v>4.638898849487305</v>
       </c>
       <c r="H27" t="n">
-        <v>4.807475090026855</v>
+        <v>4.946153163909912</v>
       </c>
       <c r="I27" t="n">
-        <v>5.195481538772583</v>
+        <v>4.645903587341309</v>
       </c>
       <c r="J27" t="n">
-        <v>4.839385271072388</v>
+        <v>4.94464111328125</v>
       </c>
       <c r="K27" t="n">
-        <v>4.661343812942505</v>
+        <v>5.214413166046143</v>
       </c>
       <c r="L27" t="n">
-        <v>4.986246061325073</v>
+        <v>4.895222210884095</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>4.171135425567627</v>
+        <v>4.084376811981201</v>
       </c>
       <c r="C28" t="n">
-        <v>4.050457954406738</v>
+        <v>4.058944940567017</v>
       </c>
       <c r="D28" t="n">
-        <v>4.11477255821228</v>
+        <v>4.148720979690552</v>
       </c>
       <c r="E28" t="n">
-        <v>4.126783609390259</v>
+        <v>4.329718828201294</v>
       </c>
       <c r="F28" t="n">
-        <v>4.325216054916382</v>
+        <v>3.903354644775391</v>
       </c>
       <c r="G28" t="n">
-        <v>4.266389846801758</v>
+        <v>4.186587572097778</v>
       </c>
       <c r="H28" t="n">
-        <v>3.994587421417236</v>
+        <v>4.115783929824829</v>
       </c>
       <c r="I28" t="n">
-        <v>4.256934404373169</v>
+        <v>4.115790128707886</v>
       </c>
       <c r="J28" t="n">
-        <v>4.20504093170166</v>
+        <v>4.160167455673218</v>
       </c>
       <c r="K28" t="n">
-        <v>4.123745679855347</v>
+        <v>4.061418533325195</v>
       </c>
       <c r="L28" t="n">
-        <v>4.163506388664246</v>
+        <v>4.116486382484436</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>4.151666879653931</v>
+        <v>4.492819309234619</v>
       </c>
       <c r="C29" t="n">
-        <v>4.227979898452759</v>
+        <v>4.408394575119019</v>
       </c>
       <c r="D29" t="n">
-        <v>4.295330762863159</v>
+        <v>4.792049884796143</v>
       </c>
       <c r="E29" t="n">
-        <v>3.969651460647583</v>
+        <v>4.392553091049194</v>
       </c>
       <c r="F29" t="n">
-        <v>4.190595388412476</v>
+        <v>4.330756187438965</v>
       </c>
       <c r="G29" t="n">
-        <v>4.624478578567505</v>
+        <v>4.353161573410034</v>
       </c>
       <c r="H29" t="n">
-        <v>4.150695562362671</v>
+        <v>4.583062887191772</v>
       </c>
       <c r="I29" t="n">
-        <v>4.420493841171265</v>
+        <v>4.461402177810669</v>
       </c>
       <c r="J29" t="n">
-        <v>4.226978778839111</v>
+        <v>4.174123764038086</v>
       </c>
       <c r="K29" t="n">
-        <v>4.810460090637207</v>
+        <v>4.086857318878174</v>
       </c>
       <c r="L29" t="n">
-        <v>4.306833124160766</v>
+        <v>4.407518076896667</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>4.258914470672607</v>
+        <v>4.472351312637329</v>
       </c>
       <c r="C30" t="n">
-        <v>4.018529176712036</v>
+        <v>3.999585866928101</v>
       </c>
       <c r="D30" t="n">
-        <v>4.167180061340332</v>
+        <v>4.095822095870972</v>
       </c>
       <c r="E30" t="n">
-        <v>4.017529964447021</v>
+        <v>4.033486843109131</v>
       </c>
       <c r="F30" t="n">
-        <v>4.116772890090942</v>
+        <v>4.389626741409302</v>
       </c>
       <c r="G30" t="n">
-        <v>4.586061954498291</v>
+        <v>4.161172866821289</v>
       </c>
       <c r="H30" t="n">
-        <v>4.401572942733765</v>
+        <v>4.146689414978027</v>
       </c>
       <c r="I30" t="n">
-        <v>4.501773834228516</v>
+        <v>4.795538902282715</v>
       </c>
       <c r="J30" t="n">
-        <v>4.307273864746094</v>
+        <v>4.575102567672729</v>
       </c>
       <c r="K30" t="n">
-        <v>4.138706922531128</v>
+        <v>4.145712375640869</v>
       </c>
       <c r="L30" t="n">
-        <v>4.251431608200074</v>
+        <v>4.281508898735046</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>4.38158130645752</v>
+        <v>4.184110641479492</v>
       </c>
       <c r="C31" t="n">
-        <v>4.158684015274048</v>
+        <v>4.136728525161743</v>
       </c>
       <c r="D31" t="n">
-        <v>4.274362802505493</v>
+        <v>3.88740348815918</v>
       </c>
       <c r="E31" t="n">
-        <v>4.257889747619629</v>
+        <v>4.005591154098511</v>
       </c>
       <c r="F31" t="n">
-        <v>3.976644515991211</v>
+        <v>3.943217039108276</v>
       </c>
       <c r="G31" t="n">
-        <v>3.854450941085815</v>
+        <v>3.767198801040649</v>
       </c>
       <c r="H31" t="n">
-        <v>4.175612688064575</v>
+        <v>4.312018632888794</v>
       </c>
       <c r="I31" t="n">
-        <v>4.144208192825317</v>
+        <v>4.02076530456543</v>
       </c>
       <c r="J31" t="n">
-        <v>4.226974725723267</v>
+        <v>4.16439414024353</v>
       </c>
       <c r="K31" t="n">
-        <v>3.958190202713013</v>
+        <v>4.061619520187378</v>
       </c>
       <c r="L31" t="n">
-        <v>4.140859913825989</v>
+        <v>4.048304724693298</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>3.795101881027222</v>
+        <v>3.921001672744751</v>
       </c>
       <c r="C32" t="n">
-        <v>4.212028026580811</v>
+        <v>4.236194610595703</v>
       </c>
       <c r="D32" t="n">
-        <v>4.145551443099976</v>
+        <v>3.902549982070923</v>
       </c>
       <c r="E32" t="n">
-        <v>4.242200136184692</v>
+        <v>4.378325223922729</v>
       </c>
       <c r="F32" t="n">
-        <v>4.251176595687866</v>
+        <v>4.330948114395142</v>
       </c>
       <c r="G32" t="n">
-        <v>4.166355609893799</v>
+        <v>4.397850275039673</v>
       </c>
       <c r="H32" t="n">
-        <v>3.908563375473022</v>
+        <v>4.052655696868896</v>
       </c>
       <c r="I32" t="n">
-        <v>4.171356201171875</v>
+        <v>3.947421312332153</v>
       </c>
       <c r="J32" t="n">
-        <v>4.241177797317505</v>
+        <v>3.92599081993103</v>
       </c>
       <c r="K32" t="n">
-        <v>4.077099084854126</v>
+        <v>4.0805983543396</v>
       </c>
       <c r="L32" t="n">
-        <v>4.121061015129089</v>
+        <v>4.11735360622406</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>4.297019004821777</v>
+        <v>4.887048959732056</v>
       </c>
       <c r="C33" t="n">
-        <v>4.508013963699341</v>
+        <v>4.505014657974243</v>
       </c>
       <c r="D33" t="n">
-        <v>4.294551610946655</v>
+        <v>5.084556341171265</v>
       </c>
       <c r="E33" t="n">
-        <v>4.795782089233398</v>
+        <v>4.249152660369873</v>
       </c>
       <c r="F33" t="n">
-        <v>5.243619918823242</v>
+        <v>4.357884407043457</v>
       </c>
       <c r="G33" t="n">
-        <v>4.518964290618896</v>
+        <v>4.574817419052124</v>
       </c>
       <c r="H33" t="n">
-        <v>4.671610593795776</v>
+        <v>4.914958000183105</v>
       </c>
       <c r="I33" t="n">
-        <v>4.518968820571899</v>
+        <v>4.837161779403687</v>
       </c>
       <c r="J33" t="n">
-        <v>4.32346773147583</v>
+        <v>5.019189834594727</v>
       </c>
       <c r="K33" t="n">
-        <v>5.049668312072754</v>
+        <v>4.372341156005859</v>
       </c>
       <c r="L33" t="n">
-        <v>4.622166633605957</v>
+        <v>4.68021252155304</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>3.698073625564575</v>
+        <v>3.897585391998291</v>
       </c>
       <c r="C34" t="n">
-        <v>3.675618648529053</v>
+        <v>3.598843812942505</v>
       </c>
       <c r="D34" t="n">
-        <v>3.620754480361938</v>
+        <v>3.930978059768677</v>
       </c>
       <c r="E34" t="n">
-        <v>3.955956935882568</v>
+        <v>3.998284101486206</v>
       </c>
       <c r="F34" t="n">
-        <v>3.94245982170105</v>
+        <v>3.958906173706055</v>
       </c>
       <c r="G34" t="n">
-        <v>3.891587257385254</v>
+        <v>3.937461376190186</v>
       </c>
       <c r="H34" t="n">
-        <v>3.921482801437378</v>
+        <v>3.946957588195801</v>
       </c>
       <c r="I34" t="n">
-        <v>3.750428915023804</v>
+        <v>3.928494453430176</v>
       </c>
       <c r="J34" t="n">
-        <v>4.044700622558594</v>
+        <v>3.741945505142212</v>
       </c>
       <c r="K34" t="n">
-        <v>3.737967729568481</v>
+        <v>3.791329860687256</v>
       </c>
       <c r="L34" t="n">
-        <v>3.82390308380127</v>
+        <v>3.873078632354736</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>4.941405534744263</v>
+        <v>5.139393091201782</v>
       </c>
       <c r="C35" t="n">
-        <v>4.653183221817017</v>
+        <v>4.660630941390991</v>
       </c>
       <c r="D35" t="n">
-        <v>5.159607648849487</v>
+        <v>4.565841674804688</v>
       </c>
       <c r="E35" t="n">
-        <v>4.659381866455078</v>
+        <v>6.79634952545166</v>
       </c>
       <c r="F35" t="n">
-        <v>4.946611404418945</v>
+        <v>5.241353034973145</v>
       </c>
       <c r="G35" t="n">
-        <v>4.863827466964722</v>
+        <v>4.754623413085938</v>
       </c>
       <c r="H35" t="n">
-        <v>4.971539258956909</v>
+        <v>4.70625114440918</v>
       </c>
       <c r="I35" t="n">
-        <v>4.620955467224121</v>
+        <v>5.141128778457642</v>
       </c>
       <c r="J35" t="n">
-        <v>5.034480094909668</v>
+        <v>5.184518575668335</v>
       </c>
       <c r="K35" t="n">
-        <v>5.105211734771729</v>
+        <v>5.651290416717529</v>
       </c>
       <c r="L35" t="n">
-        <v>4.895620369911194</v>
+        <v>5.184138059616089</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>3.442023277282715</v>
+        <v>3.452516794204712</v>
       </c>
       <c r="C36" t="n">
-        <v>3.76519775390625</v>
+        <v>3.833013534545898</v>
       </c>
       <c r="D36" t="n">
-        <v>3.792598724365234</v>
+        <v>3.787135601043701</v>
       </c>
       <c r="E36" t="n">
-        <v>3.500372409820557</v>
+        <v>4.012565612792969</v>
       </c>
       <c r="F36" t="n">
-        <v>3.807093858718872</v>
+        <v>3.532291412353516</v>
       </c>
       <c r="G36" t="n">
-        <v>3.582669496536255</v>
+        <v>3.64551568031311</v>
       </c>
       <c r="H36" t="n">
-        <v>3.531295776367188</v>
+        <v>3.593685388565063</v>
       </c>
       <c r="I36" t="n">
-        <v>3.577688694000244</v>
+        <v>3.638023853302002</v>
       </c>
       <c r="J36" t="n">
-        <v>3.81008505821228</v>
+        <v>3.671993732452393</v>
       </c>
       <c r="K36" t="n">
-        <v>3.661455869674683</v>
+        <v>3.613951206207275</v>
       </c>
       <c r="L36" t="n">
-        <v>3.647048091888428</v>
+        <v>3.678069281578064</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>4.644390821456909</v>
+        <v>5.101479053497314</v>
       </c>
       <c r="C37" t="n">
-        <v>4.614982604980469</v>
+        <v>4.513009309768677</v>
       </c>
       <c r="D37" t="n">
-        <v>4.954591512680054</v>
+        <v>4.486063241958618</v>
       </c>
       <c r="E37" t="n">
-        <v>4.55814266204834</v>
+        <v>4.548423528671265</v>
       </c>
       <c r="F37" t="n">
-        <v>4.425410747528076</v>
+        <v>4.666082143783569</v>
       </c>
       <c r="G37" t="n">
-        <v>4.393916606903076</v>
+        <v>4.489053964614868</v>
       </c>
       <c r="H37" t="n">
-        <v>4.407757759094238</v>
+        <v>4.528946876525879</v>
       </c>
       <c r="I37" t="n">
-        <v>4.49403715133667</v>
+        <v>4.896598815917969</v>
       </c>
       <c r="J37" t="n">
-        <v>4.386298418045044</v>
+        <v>4.399788618087769</v>
       </c>
       <c r="K37" t="n">
-        <v>4.514004230499268</v>
+        <v>4.231200933456421</v>
       </c>
       <c r="L37" t="n">
-        <v>4.539353251457214</v>
+        <v>4.586064648628235</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>5.591840267181396</v>
+        <v>4.83870267868042</v>
       </c>
       <c r="C38" t="n">
-        <v>4.714468240737915</v>
+        <v>4.402774572372437</v>
       </c>
       <c r="D38" t="n">
-        <v>4.428691148757935</v>
+        <v>4.472108840942383</v>
       </c>
       <c r="E38" t="n">
-        <v>4.518979072570801</v>
+        <v>4.435694217681885</v>
       </c>
       <c r="F38" t="n">
-        <v>4.741890907287598</v>
+        <v>4.726456880569458</v>
       </c>
       <c r="G38" t="n">
-        <v>4.801774024963379</v>
+        <v>4.724442958831787</v>
       </c>
       <c r="H38" t="n">
-        <v>4.400781631469727</v>
+        <v>4.596274375915527</v>
       </c>
       <c r="I38" t="n">
-        <v>4.465621709823608</v>
+        <v>4.604285001754761</v>
       </c>
       <c r="J38" t="n">
-        <v>4.483074426651001</v>
+        <v>4.406757593154907</v>
       </c>
       <c r="K38" t="n">
-        <v>4.417724609375</v>
+        <v>4.985289573669434</v>
       </c>
       <c r="L38" t="n">
-        <v>4.656484603881836</v>
+        <v>4.6192786693573</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>4.126975536346436</v>
+        <v>3.773376226425171</v>
       </c>
       <c r="C39" t="n">
-        <v>3.782340288162231</v>
+        <v>3.714026212692261</v>
       </c>
       <c r="D39" t="n">
-        <v>4.132961511611938</v>
+        <v>3.742433547973633</v>
       </c>
       <c r="E39" t="n">
-        <v>3.558714628219604</v>
+        <v>4.106021165847778</v>
       </c>
       <c r="F39" t="n">
-        <v>3.80510687828064</v>
+        <v>3.928497076034546</v>
       </c>
       <c r="G39" t="n">
-        <v>3.875895738601685</v>
+        <v>4.222743034362793</v>
       </c>
       <c r="H39" t="n">
-        <v>4.046956300735474</v>
+        <v>3.819265365600586</v>
       </c>
       <c r="I39" t="n">
-        <v>3.924270629882812</v>
+        <v>3.93247652053833</v>
       </c>
       <c r="J39" t="n">
-        <v>4.293315649032593</v>
+        <v>3.956411838531494</v>
       </c>
       <c r="K39" t="n">
-        <v>3.762696981430054</v>
+        <v>3.823755741119385</v>
       </c>
       <c r="L39" t="n">
-        <v>3.930923414230347</v>
+        <v>3.901900672912598</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>4.481835603713989</v>
+        <v>4.637177705764771</v>
       </c>
       <c r="C40" t="n">
-        <v>4.493794202804565</v>
+        <v>4.370373249053955</v>
       </c>
       <c r="D40" t="n">
-        <v>4.443142175674438</v>
+        <v>4.676581621170044</v>
       </c>
       <c r="E40" t="n">
-        <v>4.623213768005371</v>
+        <v>4.514029264450073</v>
       </c>
       <c r="F40" t="n">
-        <v>4.298540353775024</v>
+        <v>4.288567066192627</v>
       </c>
       <c r="G40" t="n">
-        <v>6.739392995834351</v>
+        <v>4.611229181289673</v>
       </c>
       <c r="H40" t="n">
-        <v>5.455409049987793</v>
+        <v>4.740464925765991</v>
       </c>
       <c r="I40" t="n">
-        <v>5.218474626541138</v>
+        <v>4.431694269180298</v>
       </c>
       <c r="J40" t="n">
-        <v>5.525063991546631</v>
+        <v>4.692537546157837</v>
       </c>
       <c r="K40" t="n">
-        <v>4.418027877807617</v>
+        <v>4.313497066497803</v>
       </c>
       <c r="L40" t="n">
-        <v>4.969689464569091</v>
+        <v>4.527615189552307</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>6.064273595809937</v>
+        <v>4.458132982254028</v>
       </c>
       <c r="C41" t="n">
-        <v>4.41637659072876</v>
+        <v>4.547900676727295</v>
       </c>
       <c r="D41" t="n">
-        <v>4.896299839019775</v>
+        <v>4.453134775161743</v>
       </c>
       <c r="E41" t="n">
-        <v>4.242610692977905</v>
+        <v>4.599289894104004</v>
       </c>
       <c r="F41" t="n">
-        <v>4.306338787078857</v>
+        <v>4.215254068374634</v>
       </c>
       <c r="G41" t="n">
-        <v>4.476655721664429</v>
+        <v>4.2930588722229</v>
       </c>
       <c r="H41" t="n">
-        <v>4.377533197402954</v>
+        <v>4.229707717895508</v>
       </c>
       <c r="I41" t="n">
-        <v>4.270082950592041</v>
+        <v>4.410744905471802</v>
       </c>
       <c r="J41" t="n">
-        <v>4.798164367675781</v>
+        <v>4.287065744400024</v>
       </c>
       <c r="K41" t="n">
-        <v>4.524771690368652</v>
+        <v>4.235842704772949</v>
       </c>
       <c r="L41" t="n">
-        <v>4.637310743331909</v>
+        <v>4.373013234138488</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>4.367316246032715</v>
+        <v>4.393086671829224</v>
       </c>
       <c r="C42" t="n">
-        <v>4.221251487731934</v>
+        <v>4.323246955871582</v>
       </c>
       <c r="D42" t="n">
-        <v>4.525678157806396</v>
+        <v>4.312307357788086</v>
       </c>
       <c r="E42" t="n">
-        <v>4.582574605941772</v>
+        <v>4.131751775741577</v>
       </c>
       <c r="F42" t="n">
-        <v>4.225322484970093</v>
+        <v>4.085875034332275</v>
       </c>
       <c r="G42" t="n">
-        <v>4.729886293411255</v>
+        <v>4.154682397842407</v>
       </c>
       <c r="H42" t="n">
-        <v>4.428421258926392</v>
+        <v>4.079888820648193</v>
       </c>
       <c r="I42" t="n">
-        <v>4.867672204971313</v>
+        <v>4.328224897384644</v>
       </c>
       <c r="J42" t="n">
-        <v>4.301209449768066</v>
+        <v>4.439451456069946</v>
       </c>
       <c r="K42" t="n">
-        <v>4.452571630477905</v>
+        <v>4.323238134384155</v>
       </c>
       <c r="L42" t="n">
-        <v>4.470190382003784</v>
+        <v>4.257175350189209</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>4.763832807540894</v>
+        <v>4.724408388137817</v>
       </c>
       <c r="C43" t="n">
-        <v>5.129714488983154</v>
+        <v>4.385305404663086</v>
       </c>
       <c r="D43" t="n">
-        <v>4.574394702911377</v>
+        <v>4.579319715499878</v>
       </c>
       <c r="E43" t="n">
-        <v>4.729371547698975</v>
+        <v>4.479080677032471</v>
       </c>
       <c r="F43" t="n">
-        <v>4.555794954299927</v>
+        <v>4.687031984329224</v>
       </c>
       <c r="G43" t="n">
-        <v>5.156594276428223</v>
+        <v>5.097538948059082</v>
       </c>
       <c r="H43" t="n">
-        <v>4.798900127410889</v>
+        <v>4.517967700958252</v>
       </c>
       <c r="I43" t="n">
-        <v>4.733113288879395</v>
+        <v>4.471099853515625</v>
       </c>
       <c r="J43" t="n">
-        <v>4.8997642993927</v>
+        <v>4.442651748657227</v>
       </c>
       <c r="K43" t="n">
-        <v>5.005243062973022</v>
+        <v>4.306507110595703</v>
       </c>
       <c r="L43" t="n">
-        <v>4.834672355651856</v>
+        <v>4.569091153144837</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>4.476581811904907</v>
+        <v>4.343915224075317</v>
       </c>
       <c r="C44" t="n">
-        <v>4.113120794296265</v>
+        <v>4.059681415557861</v>
       </c>
       <c r="D44" t="n">
-        <v>4.166948318481445</v>
+        <v>5.015221357345581</v>
       </c>
       <c r="E44" t="n">
-        <v>4.153094530105591</v>
+        <v>4.324998140335083</v>
       </c>
       <c r="F44" t="n">
-        <v>4.358477354049683</v>
+        <v>4.191795587539673</v>
       </c>
       <c r="G44" t="n">
-        <v>4.533000230789185</v>
+        <v>4.200282573699951</v>
       </c>
       <c r="H44" t="n">
-        <v>4.186561107635498</v>
+        <v>4.509006023406982</v>
       </c>
       <c r="I44" t="n">
-        <v>4.258862972259521</v>
+        <v>4.122974157333374</v>
       </c>
       <c r="J44" t="n">
-        <v>4.281290531158447</v>
+        <v>4.582308769226074</v>
       </c>
       <c r="K44" t="n">
-        <v>4.134181022644043</v>
+        <v>4.403785943984985</v>
       </c>
       <c r="L44" t="n">
-        <v>4.266211867332458</v>
+        <v>4.375396919250488</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>4.06312084197998</v>
+        <v>4.044209241867065</v>
       </c>
       <c r="C45" t="n">
-        <v>4.13821268081665</v>
+        <v>4.075597524642944</v>
       </c>
       <c r="D45" t="n">
-        <v>4.386143445968628</v>
+        <v>3.886599063873291</v>
       </c>
       <c r="E45" t="n">
-        <v>4.256901979446411</v>
+        <v>4.200281381607056</v>
       </c>
       <c r="F45" t="n">
-        <v>4.0294189453125</v>
+        <v>4.145914316177368</v>
       </c>
       <c r="G45" t="n">
-        <v>4.208676338195801</v>
+        <v>4.451154947280884</v>
       </c>
       <c r="H45" t="n">
-        <v>4.354820013046265</v>
+        <v>3.995815992355347</v>
       </c>
       <c r="I45" t="n">
-        <v>4.13960337638855</v>
+        <v>4.05764365196228</v>
       </c>
       <c r="J45" t="n">
-        <v>4.196491241455078</v>
+        <v>4.069139242172241</v>
       </c>
       <c r="K45" t="n">
-        <v>4.170922756195068</v>
+        <v>4.144976854324341</v>
       </c>
       <c r="L45" t="n">
-        <v>4.194431161880493</v>
+        <v>4.107133221626282</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>4.306963443756104</v>
+        <v>4.219233274459839</v>
       </c>
       <c r="C46" t="n">
-        <v>4.200486183166504</v>
+        <v>4.169379472732544</v>
       </c>
       <c r="D46" t="n">
-        <v>4.112522840499878</v>
+        <v>4.161880016326904</v>
       </c>
       <c r="E46" t="n">
-        <v>4.232023954391479</v>
+        <v>4.005804300308228</v>
       </c>
       <c r="F46" t="n">
-        <v>4.516276121139526</v>
+        <v>4.395804643630981</v>
       </c>
       <c r="G46" t="n">
-        <v>3.971285343170166</v>
+        <v>4.483062744140625</v>
       </c>
       <c r="H46" t="n">
-        <v>4.372519969940186</v>
+        <v>4.083080291748047</v>
       </c>
       <c r="I46" t="n">
-        <v>4.438383817672729</v>
+        <v>4.628197431564331</v>
       </c>
       <c r="J46" t="n">
-        <v>4.454649209976196</v>
+        <v>4.551895141601562</v>
       </c>
       <c r="K46" t="n">
-        <v>4.254840135574341</v>
+        <v>4.105033397674561</v>
       </c>
       <c r="L46" t="n">
-        <v>4.285995101928711</v>
+        <v>4.280337071418762</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>5.054869890213013</v>
+        <v>5.460625410079956</v>
       </c>
       <c r="C47" t="n">
-        <v>4.523228406906128</v>
+        <v>4.735411167144775</v>
       </c>
       <c r="D47" t="n">
-        <v>4.762272834777832</v>
+        <v>4.851149320602417</v>
       </c>
       <c r="E47" t="n">
-        <v>4.368190765380859</v>
+        <v>4.535933494567871</v>
       </c>
       <c r="F47" t="n">
-        <v>4.177456140518188</v>
+        <v>4.375325679779053</v>
       </c>
       <c r="G47" t="n">
-        <v>4.425575017929077</v>
+        <v>4.186833143234253</v>
       </c>
       <c r="H47" t="n">
-        <v>4.566431283950806</v>
+        <v>4.40775728225708</v>
       </c>
       <c r="I47" t="n">
-        <v>4.51961612701416</v>
+        <v>4.460142612457275</v>
       </c>
       <c r="J47" t="n">
-        <v>4.540579795837402</v>
+        <v>4.809715270996094</v>
       </c>
       <c r="K47" t="n">
-        <v>4.902342796325684</v>
+        <v>4.902994871139526</v>
       </c>
       <c r="L47" t="n">
-        <v>4.584056305885315</v>
+        <v>4.67258882522583</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>4.451871871948242</v>
+        <v>4.315496683120728</v>
       </c>
       <c r="C48" t="n">
-        <v>4.305331945419312</v>
+        <v>4.527010440826416</v>
       </c>
       <c r="D48" t="n">
-        <v>4.707366943359375</v>
+        <v>4.394803285598755</v>
       </c>
       <c r="E48" t="n">
-        <v>4.428887128829956</v>
+        <v>4.95491623878479</v>
       </c>
       <c r="F48" t="n">
-        <v>4.61860728263855</v>
+        <v>4.134959936141968</v>
       </c>
       <c r="G48" t="n">
-        <v>4.812867879867554</v>
+        <v>4.416245460510254</v>
       </c>
       <c r="H48" t="n">
-        <v>4.494068384170532</v>
+        <v>4.19878101348877</v>
       </c>
       <c r="I48" t="n">
-        <v>4.669947624206543</v>
+        <v>4.212265014648438</v>
       </c>
       <c r="J48" t="n">
-        <v>4.918102741241455</v>
+        <v>4.401779890060425</v>
       </c>
       <c r="K48" t="n">
-        <v>4.880361318588257</v>
+        <v>4.389790296554565</v>
       </c>
       <c r="L48" t="n">
-        <v>4.628741312026977</v>
+        <v>4.394604825973511</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>5.328684329986572</v>
+        <v>4.588301658630371</v>
       </c>
       <c r="C49" t="n">
-        <v>4.804047107696533</v>
+        <v>4.518973112106323</v>
       </c>
       <c r="D49" t="n">
-        <v>5.065278053283691</v>
+        <v>4.137952566146851</v>
       </c>
       <c r="E49" t="n">
-        <v>4.602153062820435</v>
+        <v>4.515989303588867</v>
       </c>
       <c r="F49" t="n">
-        <v>4.792337656021118</v>
+        <v>5.011216163635254</v>
       </c>
       <c r="G49" t="n">
-        <v>4.884902238845825</v>
+        <v>4.734951734542847</v>
       </c>
       <c r="H49" t="n">
-        <v>4.748729228973389</v>
+        <v>4.615256786346436</v>
       </c>
       <c r="I49" t="n">
-        <v>5.247962236404419</v>
+        <v>4.549909591674805</v>
       </c>
       <c r="J49" t="n">
-        <v>5.133180379867554</v>
+        <v>4.563365936279297</v>
       </c>
       <c r="K49" t="n">
-        <v>4.813074588775635</v>
+        <v>4.667103052139282</v>
       </c>
       <c r="L49" t="n">
-        <v>4.942034888267517</v>
+        <v>4.590301990509033</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>3.726743221282959</v>
+        <v>3.517541408538818</v>
       </c>
       <c r="C50" t="n">
-        <v>3.92306113243103</v>
+        <v>3.806288242340088</v>
       </c>
       <c r="D50" t="n">
-        <v>3.797461032867432</v>
+        <v>3.626253604888916</v>
       </c>
       <c r="E50" t="n">
-        <v>3.681251764297485</v>
+        <v>3.606806516647339</v>
       </c>
       <c r="F50" t="n">
-        <v>3.991901874542236</v>
+        <v>3.599308490753174</v>
       </c>
       <c r="G50" t="n">
-        <v>3.794443607330322</v>
+        <v>3.796861886978149</v>
       </c>
       <c r="H50" t="n">
-        <v>3.682687044143677</v>
+        <v>3.573337554931641</v>
       </c>
       <c r="I50" t="n">
-        <v>3.638679027557373</v>
+        <v>3.564713716506958</v>
       </c>
       <c r="J50" t="n">
-        <v>3.681167840957642</v>
+        <v>3.835000276565552</v>
       </c>
       <c r="K50" t="n">
-        <v>3.819395542144775</v>
+        <v>3.571695804595947</v>
       </c>
       <c r="L50" t="n">
-        <v>3.773679208755493</v>
+        <v>3.649780750274658</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>4.645257711410522</v>
+        <v>4.719201326370239</v>
       </c>
       <c r="C51" t="n">
-        <v>4.545559167861938</v>
+        <v>4.39656662940979</v>
       </c>
       <c r="D51" t="n">
-        <v>4.583996057510376</v>
+        <v>4.655874490737915</v>
       </c>
       <c r="E51" t="n">
-        <v>4.386234521865845</v>
+        <v>4.433471202850342</v>
       </c>
       <c r="F51" t="n">
-        <v>4.131996870040894</v>
+        <v>4.391556262969971</v>
       </c>
       <c r="G51" t="n">
-        <v>4.214277029037476</v>
+        <v>4.306280374526978</v>
       </c>
       <c r="H51" t="n">
-        <v>4.382513761520386</v>
+        <v>4.277365922927856</v>
       </c>
       <c r="I51" t="n">
-        <v>5.11290431022644</v>
+        <v>3.986615419387817</v>
       </c>
       <c r="J51" t="n">
-        <v>4.968940019607544</v>
+        <v>4.518752574920654</v>
       </c>
       <c r="K51" t="n">
-        <v>4.254076957702637</v>
+        <v>4.737199068069458</v>
       </c>
       <c r="L51" t="n">
-        <v>4.522575640678406</v>
+        <v>4.442288327217102</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4.447328886985779</v>
+        <v>4.386521120071411</v>
       </c>
       <c r="C52" t="n">
-        <v>4.394654412269592</v>
+        <v>4.352992720603943</v>
       </c>
       <c r="D52" t="n">
-        <v>4.406770076751709</v>
+        <v>4.351500868797302</v>
       </c>
       <c r="E52" t="n">
-        <v>4.343036665916443</v>
+        <v>4.386967916488647</v>
       </c>
       <c r="F52" t="n">
-        <v>4.361461420059204</v>
+        <v>4.375260081291199</v>
       </c>
       <c r="G52" t="n">
-        <v>4.438050718307495</v>
+        <v>4.33856162071228</v>
       </c>
       <c r="H52" t="n">
-        <v>4.381503734588623</v>
+        <v>4.354555878639221</v>
       </c>
       <c r="I52" t="n">
-        <v>4.405130243301391</v>
+        <v>4.357239050865173</v>
       </c>
       <c r="J52" t="n">
-        <v>4.434468231201172</v>
+        <v>4.367395634651184</v>
       </c>
       <c r="K52" t="n">
-        <v>4.439879007339478</v>
+        <v>4.348528790473938</v>
       </c>
       <c r="L52" t="n">
-        <v>4.405228339672089</v>
+        <v>4.361952368259431</v>
       </c>
     </row>
   </sheetData>
